--- a/TestCases/Notification_TestCase.xlsx
+++ b/TestCases/Notification_TestCase.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\DoAnNganh\SpringMediCareWeb-Selenium-Testing\TestCases\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8C8CA5BF-201F-4318-9793-2E5069753A06}" xr6:coauthVersionLast="36" xr6:coauthVersionMax="36" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D49FAF3A-CEAE-4E5D-8DF6-9C7816123175}" xr6:coauthVersionLast="36" xr6:coauthVersionMax="36" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="0" yWindow="0" windowWidth="23040" windowHeight="8940" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -23,7 +23,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="95" uniqueCount="84">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="99" uniqueCount="86">
   <si>
     <t>TEST CASE</t>
   </si>
@@ -285,6 +285,9 @@
     <t>Không phát sinh thông báo đơn thuốc cho Patient sau khi Doctor lưu đơn thuốc mới.</t>
   </si>
   <si>
+    <t>TCNotificationRetest6_1, TCNotificationRetest6_2</t>
+  </si>
+  <si>
     <t xml:space="preserve">5. Kiểm tra thông báo kết quả xét nghiệm
 </t>
   </si>
@@ -315,10 +318,13 @@
 Thời gian thông báo được ghi nhận và hiển thị.</t>
   </si>
   <si>
-    <t>TCNotification7_1, TCNotification7_2, TCNotification7_3</t>
+    <t>TCNotification7_1, TCNotification7_2</t>
   </si>
   <si>
     <t>Không phát sinh thông báo kết quả xét nghiệm cho Patient sau khi Doctor thêm kết quả xét nghiệm.</t>
+  </si>
+  <si>
+    <t>TCNotificationRetest7_1, TCNotificationRetest7_2</t>
   </si>
   <si>
     <t>6. Kiểm tra thông báo khi dữ liệu khám bệnh được thay đổi</t>
@@ -394,7 +400,7 @@
   <numFmts count="1">
     <numFmt numFmtId="165" formatCode="d\-m"/>
   </numFmts>
-  <fonts count="11" x14ac:knownFonts="1">
+  <fonts count="12" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color rgb="FF000000"/>
@@ -442,6 +448,12 @@
       <sz val="11"/>
       <color rgb="FFFF0000"/>
       <name val="Tahoma"/>
+    </font>
+    <font>
+      <u/>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="Arial"/>
     </font>
     <font>
       <u/>
@@ -624,7 +636,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="43">
+  <cellXfs count="44">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
     <xf numFmtId="0" fontId="2" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1"/>
     <xf numFmtId="0" fontId="3" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1"/>
@@ -668,16 +680,19 @@
     <xf numFmtId="0" fontId="3" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="top"/>
     </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="top"/>
+    </xf>
     <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="top"/>
     </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1"/>
@@ -949,9 +964,9 @@
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="30"/>
-      <c r="C1" s="31"/>
-      <c r="D1" s="31"/>
+      <c r="B1" s="31"/>
+      <c r="C1" s="32"/>
+      <c r="D1" s="32"/>
       <c r="E1" s="2"/>
       <c r="F1" s="2"/>
       <c r="G1" s="2"/>
@@ -978,9 +993,9 @@
     </row>
     <row r="2" spans="1:27" ht="13.8" x14ac:dyDescent="0.25">
       <c r="A2" s="2"/>
-      <c r="B2" s="29"/>
-      <c r="C2" s="29"/>
-      <c r="D2" s="29"/>
+      <c r="B2" s="30"/>
+      <c r="C2" s="30"/>
+      <c r="D2" s="30"/>
       <c r="E2" s="2"/>
       <c r="F2" s="2"/>
       <c r="G2" s="2"/>
@@ -1009,11 +1024,11 @@
       <c r="A3" s="4" t="s">
         <v>1</v>
       </c>
-      <c r="B3" s="32" t="s">
+      <c r="B3" s="33" t="s">
         <v>2</v>
       </c>
-      <c r="C3" s="25"/>
-      <c r="D3" s="27"/>
+      <c r="C3" s="26"/>
+      <c r="D3" s="28"/>
       <c r="E3" s="2"/>
       <c r="F3" s="2"/>
       <c r="G3" s="2"/>
@@ -1042,11 +1057,11 @@
       <c r="A4" s="4" t="s">
         <v>3</v>
       </c>
-      <c r="B4" s="33" t="s">
+      <c r="B4" s="34" t="s">
         <v>20</v>
       </c>
-      <c r="C4" s="25"/>
-      <c r="D4" s="27"/>
+      <c r="C4" s="26"/>
+      <c r="D4" s="28"/>
       <c r="E4" s="2"/>
       <c r="F4" s="2"/>
       <c r="G4" s="2"/>
@@ -1075,11 +1090,11 @@
       <c r="A5" s="4" t="s">
         <v>4</v>
       </c>
-      <c r="B5" s="32" t="s">
+      <c r="B5" s="33" t="s">
         <v>21</v>
       </c>
-      <c r="C5" s="25"/>
-      <c r="D5" s="27"/>
+      <c r="C5" s="26"/>
+      <c r="D5" s="28"/>
       <c r="E5" s="2"/>
       <c r="F5" s="2"/>
       <c r="G5" s="2"/>
@@ -1208,39 +1223,39 @@
       <c r="AA8" s="3"/>
     </row>
     <row r="9" spans="1:27" ht="13.8" x14ac:dyDescent="0.25">
-      <c r="A9" s="34" t="s">
+      <c r="A9" s="35" t="s">
         <v>9</v>
       </c>
-      <c r="B9" s="35" t="s">
+      <c r="B9" s="36" t="s">
         <v>10</v>
       </c>
-      <c r="C9" s="34" t="s">
+      <c r="C9" s="35" t="s">
         <v>11</v>
       </c>
-      <c r="D9" s="36" t="s">
+      <c r="D9" s="37" t="s">
         <v>12</v>
       </c>
-      <c r="E9" s="31"/>
-      <c r="F9" s="31"/>
-      <c r="G9" s="34" t="s">
+      <c r="E9" s="32"/>
+      <c r="F9" s="32"/>
+      <c r="G9" s="35" t="s">
         <v>13</v>
       </c>
-      <c r="H9" s="37" t="s">
+      <c r="H9" s="38" t="s">
         <v>14</v>
       </c>
-      <c r="I9" s="37" t="s">
+      <c r="I9" s="38" t="s">
         <v>15</v>
       </c>
-      <c r="J9" s="37" t="s">
+      <c r="J9" s="38" t="s">
         <v>16</v>
       </c>
-      <c r="K9" s="37" t="s">
+      <c r="K9" s="38" t="s">
         <v>17</v>
       </c>
-      <c r="L9" s="37" t="s">
+      <c r="L9" s="38" t="s">
         <v>18</v>
       </c>
-      <c r="M9" s="37" t="s">
+      <c r="M9" s="38" t="s">
         <v>19</v>
       </c>
       <c r="N9" s="3"/>
@@ -1259,19 +1274,19 @@
       <c r="AA9" s="3"/>
     </row>
     <row r="10" spans="1:27" ht="13.8" x14ac:dyDescent="0.25">
-      <c r="A10" s="26"/>
-      <c r="B10" s="26"/>
-      <c r="C10" s="26"/>
-      <c r="D10" s="28"/>
-      <c r="E10" s="29"/>
-      <c r="F10" s="29"/>
-      <c r="G10" s="26"/>
-      <c r="H10" s="26"/>
-      <c r="I10" s="26"/>
-      <c r="J10" s="26"/>
-      <c r="K10" s="26"/>
-      <c r="L10" s="26"/>
-      <c r="M10" s="26"/>
+      <c r="A10" s="27"/>
+      <c r="B10" s="27"/>
+      <c r="C10" s="27"/>
+      <c r="D10" s="29"/>
+      <c r="E10" s="30"/>
+      <c r="F10" s="30"/>
+      <c r="G10" s="27"/>
+      <c r="H10" s="27"/>
+      <c r="I10" s="27"/>
+      <c r="J10" s="27"/>
+      <c r="K10" s="27"/>
+      <c r="L10" s="27"/>
+      <c r="M10" s="27"/>
       <c r="N10" s="3"/>
       <c r="O10" s="3"/>
       <c r="P10" s="3"/>
@@ -1289,18 +1304,18 @@
     </row>
     <row r="11" spans="1:27" ht="13.8" x14ac:dyDescent="0.25">
       <c r="A11" s="13"/>
-      <c r="B11" s="38"/>
-      <c r="C11" s="25"/>
-      <c r="D11" s="25"/>
-      <c r="E11" s="25"/>
-      <c r="F11" s="25"/>
-      <c r="G11" s="25"/>
-      <c r="H11" s="25"/>
-      <c r="I11" s="25"/>
-      <c r="J11" s="25"/>
-      <c r="K11" s="25"/>
-      <c r="L11" s="25"/>
-      <c r="M11" s="25"/>
+      <c r="B11" s="39"/>
+      <c r="C11" s="26"/>
+      <c r="D11" s="26"/>
+      <c r="E11" s="26"/>
+      <c r="F11" s="26"/>
+      <c r="G11" s="26"/>
+      <c r="H11" s="26"/>
+      <c r="I11" s="26"/>
+      <c r="J11" s="26"/>
+      <c r="K11" s="26"/>
+      <c r="L11" s="26"/>
+      <c r="M11" s="26"/>
       <c r="N11" s="3"/>
       <c r="O11" s="3"/>
       <c r="P11" s="3"/>
@@ -1317,21 +1332,21 @@
       <c r="AA11" s="3"/>
     </row>
     <row r="12" spans="1:27" ht="13.8" x14ac:dyDescent="0.25">
-      <c r="A12" s="39" t="s">
+      <c r="A12" s="40" t="s">
         <v>22</v>
       </c>
-      <c r="B12" s="25"/>
-      <c r="C12" s="25"/>
-      <c r="D12" s="25"/>
-      <c r="E12" s="25"/>
-      <c r="F12" s="25"/>
-      <c r="G12" s="25"/>
-      <c r="H12" s="25"/>
-      <c r="I12" s="25"/>
-      <c r="J12" s="25"/>
-      <c r="K12" s="25"/>
-      <c r="L12" s="25"/>
-      <c r="M12" s="27"/>
+      <c r="B12" s="26"/>
+      <c r="C12" s="26"/>
+      <c r="D12" s="26"/>
+      <c r="E12" s="26"/>
+      <c r="F12" s="26"/>
+      <c r="G12" s="26"/>
+      <c r="H12" s="26"/>
+      <c r="I12" s="26"/>
+      <c r="J12" s="26"/>
+      <c r="K12" s="26"/>
+      <c r="L12" s="26"/>
+      <c r="M12" s="28"/>
       <c r="N12" s="3"/>
       <c r="O12" s="3"/>
       <c r="P12" s="3"/>
@@ -1357,11 +1372,11 @@
       <c r="C13" s="16" t="s">
         <v>25</v>
       </c>
-      <c r="D13" s="40" t="s">
+      <c r="D13" s="41" t="s">
         <v>26</v>
       </c>
-      <c r="E13" s="25"/>
-      <c r="F13" s="25"/>
+      <c r="E13" s="26"/>
+      <c r="F13" s="26"/>
       <c r="G13" s="17" t="s">
         <v>27</v>
       </c>
@@ -1402,11 +1417,11 @@
       <c r="C14" s="16" t="s">
         <v>31</v>
       </c>
-      <c r="D14" s="40" t="s">
+      <c r="D14" s="41" t="s">
         <v>32</v>
       </c>
-      <c r="E14" s="25"/>
-      <c r="F14" s="25"/>
+      <c r="E14" s="26"/>
+      <c r="F14" s="26"/>
       <c r="G14" s="17" t="s">
         <v>33</v>
       </c>
@@ -1444,21 +1459,21 @@
       <c r="AA14" s="3"/>
     </row>
     <row r="15" spans="1:27" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A15" s="39" t="s">
+      <c r="A15" s="40" t="s">
         <v>36</v>
       </c>
-      <c r="B15" s="25"/>
-      <c r="C15" s="25"/>
-      <c r="D15" s="25"/>
-      <c r="E15" s="25"/>
-      <c r="F15" s="25"/>
-      <c r="G15" s="25"/>
-      <c r="H15" s="25"/>
-      <c r="I15" s="25"/>
-      <c r="J15" s="25"/>
-      <c r="K15" s="25"/>
-      <c r="L15" s="25"/>
-      <c r="M15" s="27"/>
+      <c r="B15" s="26"/>
+      <c r="C15" s="26"/>
+      <c r="D15" s="26"/>
+      <c r="E15" s="26"/>
+      <c r="F15" s="26"/>
+      <c r="G15" s="26"/>
+      <c r="H15" s="26"/>
+      <c r="I15" s="26"/>
+      <c r="J15" s="26"/>
+      <c r="K15" s="26"/>
+      <c r="L15" s="26"/>
+      <c r="M15" s="28"/>
       <c r="N15" s="3"/>
       <c r="O15" s="3"/>
       <c r="P15" s="3"/>
@@ -1484,11 +1499,11 @@
       <c r="C16" s="16" t="s">
         <v>39</v>
       </c>
-      <c r="D16" s="40" t="s">
+      <c r="D16" s="41" t="s">
         <v>40</v>
       </c>
-      <c r="E16" s="25"/>
-      <c r="F16" s="25"/>
+      <c r="E16" s="26"/>
+      <c r="F16" s="26"/>
       <c r="G16" s="17" t="s">
         <v>41</v>
       </c>
@@ -1526,21 +1541,21 @@
       <c r="AA16" s="3"/>
     </row>
     <row r="17" spans="1:27" ht="13.8" x14ac:dyDescent="0.25">
-      <c r="A17" s="39" t="s">
+      <c r="A17" s="40" t="s">
         <v>44</v>
       </c>
-      <c r="B17" s="25"/>
-      <c r="C17" s="25"/>
-      <c r="D17" s="25"/>
-      <c r="E17" s="25"/>
-      <c r="F17" s="25"/>
-      <c r="G17" s="25"/>
-      <c r="H17" s="25"/>
-      <c r="I17" s="25"/>
-      <c r="J17" s="25"/>
-      <c r="K17" s="25"/>
-      <c r="L17" s="25"/>
-      <c r="M17" s="27"/>
+      <c r="B17" s="26"/>
+      <c r="C17" s="26"/>
+      <c r="D17" s="26"/>
+      <c r="E17" s="26"/>
+      <c r="F17" s="26"/>
+      <c r="G17" s="26"/>
+      <c r="H17" s="26"/>
+      <c r="I17" s="26"/>
+      <c r="J17" s="26"/>
+      <c r="K17" s="26"/>
+      <c r="L17" s="26"/>
+      <c r="M17" s="28"/>
       <c r="N17" s="3"/>
       <c r="O17" s="3"/>
       <c r="P17" s="3"/>
@@ -1566,11 +1581,11 @@
       <c r="C18" s="16" t="s">
         <v>47</v>
       </c>
-      <c r="D18" s="40" t="s">
+      <c r="D18" s="41" t="s">
         <v>48</v>
       </c>
-      <c r="E18" s="25"/>
-      <c r="F18" s="25"/>
+      <c r="E18" s="26"/>
+      <c r="F18" s="26"/>
       <c r="G18" s="17" t="s">
         <v>49</v>
       </c>
@@ -1611,11 +1626,11 @@
       <c r="C19" s="16" t="s">
         <v>53</v>
       </c>
-      <c r="D19" s="40" t="s">
+      <c r="D19" s="41" t="s">
         <v>54</v>
       </c>
-      <c r="E19" s="25"/>
-      <c r="F19" s="25"/>
+      <c r="E19" s="26"/>
+      <c r="F19" s="26"/>
       <c r="G19" s="17" t="s">
         <v>55</v>
       </c>
@@ -1647,21 +1662,21 @@
       <c r="AA19" s="3"/>
     </row>
     <row r="20" spans="1:27" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A20" s="39" t="s">
+      <c r="A20" s="40" t="s">
         <v>57</v>
       </c>
-      <c r="B20" s="25"/>
-      <c r="C20" s="25"/>
-      <c r="D20" s="25"/>
-      <c r="E20" s="25"/>
-      <c r="F20" s="25"/>
-      <c r="G20" s="25"/>
-      <c r="H20" s="25"/>
-      <c r="I20" s="25"/>
-      <c r="J20" s="25"/>
-      <c r="K20" s="25"/>
-      <c r="L20" s="25"/>
-      <c r="M20" s="27"/>
+      <c r="B20" s="26"/>
+      <c r="C20" s="26"/>
+      <c r="D20" s="26"/>
+      <c r="E20" s="26"/>
+      <c r="F20" s="26"/>
+      <c r="G20" s="26"/>
+      <c r="H20" s="26"/>
+      <c r="I20" s="26"/>
+      <c r="J20" s="26"/>
+      <c r="K20" s="26"/>
+      <c r="L20" s="26"/>
+      <c r="M20" s="28"/>
       <c r="N20" s="3"/>
       <c r="O20" s="3"/>
       <c r="P20" s="3"/>
@@ -1687,11 +1702,11 @@
       <c r="C21" s="16" t="s">
         <v>60</v>
       </c>
-      <c r="D21" s="40" t="s">
+      <c r="D21" s="41" t="s">
         <v>61</v>
       </c>
-      <c r="E21" s="25"/>
-      <c r="F21" s="25"/>
+      <c r="E21" s="26"/>
+      <c r="F21" s="26"/>
       <c r="G21" s="17" t="s">
         <v>62</v>
       </c>
@@ -1704,9 +1719,15 @@
       <c r="J21" s="16" t="s">
         <v>63</v>
       </c>
-      <c r="K21" s="18"/>
-      <c r="L21" s="14"/>
-      <c r="M21" s="16"/>
+      <c r="K21" s="18">
+        <v>46249</v>
+      </c>
+      <c r="L21" s="14" t="s">
+        <v>5</v>
+      </c>
+      <c r="M21" s="17" t="s">
+        <v>64</v>
+      </c>
       <c r="N21" s="3"/>
       <c r="O21" s="3"/>
       <c r="P21" s="3"/>
@@ -1723,53 +1744,53 @@
       <c r="AA21" s="3"/>
     </row>
     <row r="22" spans="1:27" ht="13.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A22" s="39" t="s">
-        <v>64</v>
+      <c r="A22" s="40" t="s">
+        <v>65</v>
       </c>
-      <c r="B22" s="25"/>
-      <c r="C22" s="25"/>
-      <c r="D22" s="25"/>
-      <c r="E22" s="25"/>
-      <c r="F22" s="25"/>
-      <c r="G22" s="25"/>
-      <c r="H22" s="25"/>
-      <c r="I22" s="25"/>
-      <c r="J22" s="25"/>
-      <c r="K22" s="25"/>
-      <c r="L22" s="25"/>
-      <c r="M22" s="27"/>
-      <c r="N22" s="41"/>
-      <c r="O22" s="31"/>
-      <c r="P22" s="31"/>
-      <c r="Q22" s="31"/>
-      <c r="R22" s="31"/>
-      <c r="S22" s="31"/>
-      <c r="T22" s="31"/>
-      <c r="U22" s="31"/>
-      <c r="V22" s="31"/>
-      <c r="W22" s="31"/>
-      <c r="X22" s="31"/>
-      <c r="Y22" s="31"/>
-      <c r="Z22" s="31"/>
+      <c r="B22" s="26"/>
+      <c r="C22" s="26"/>
+      <c r="D22" s="26"/>
+      <c r="E22" s="26"/>
+      <c r="F22" s="26"/>
+      <c r="G22" s="26"/>
+      <c r="H22" s="26"/>
+      <c r="I22" s="26"/>
+      <c r="J22" s="26"/>
+      <c r="K22" s="26"/>
+      <c r="L22" s="26"/>
+      <c r="M22" s="28"/>
+      <c r="N22" s="42"/>
+      <c r="O22" s="32"/>
+      <c r="P22" s="32"/>
+      <c r="Q22" s="32"/>
+      <c r="R22" s="32"/>
+      <c r="S22" s="32"/>
+      <c r="T22" s="32"/>
+      <c r="U22" s="32"/>
+      <c r="V22" s="32"/>
+      <c r="W22" s="32"/>
+      <c r="X22" s="32"/>
+      <c r="Y22" s="32"/>
+      <c r="Z22" s="32"/>
       <c r="AA22" s="3"/>
     </row>
     <row r="23" spans="1:27" ht="155.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A23" s="14" t="s">
-        <v>65</v>
+        <v>66</v>
       </c>
       <c r="B23" s="15" t="s">
-        <v>66</v>
+        <v>67</v>
       </c>
       <c r="C23" s="16" t="s">
-        <v>67</v>
-      </c>
-      <c r="D23" s="40" t="s">
         <v>68</v>
       </c>
-      <c r="E23" s="25"/>
-      <c r="F23" s="25"/>
-      <c r="G23" s="23" t="s">
+      <c r="D23" s="41" t="s">
         <v>69</v>
+      </c>
+      <c r="E23" s="26"/>
+      <c r="F23" s="26"/>
+      <c r="G23" s="24" t="s">
+        <v>70</v>
       </c>
       <c r="H23" s="18">
         <v>46248</v>
@@ -1778,11 +1799,17 @@
         <v>7</v>
       </c>
       <c r="J23" s="16" t="s">
-        <v>70</v>
+        <v>71</v>
       </c>
-      <c r="K23" s="19"/>
-      <c r="L23" s="19"/>
-      <c r="M23" s="20"/>
+      <c r="K23" s="18">
+        <v>46249</v>
+      </c>
+      <c r="L23" s="14" t="s">
+        <v>5</v>
+      </c>
+      <c r="M23" s="21" t="s">
+        <v>72</v>
+      </c>
       <c r="N23" s="3"/>
       <c r="O23" s="3"/>
       <c r="P23" s="3"/>
@@ -1799,53 +1826,53 @@
       <c r="AA23" s="3"/>
     </row>
     <row r="24" spans="1:27" ht="13.8" x14ac:dyDescent="0.25">
-      <c r="A24" s="39" t="s">
-        <v>71</v>
+      <c r="A24" s="40" t="s">
+        <v>73</v>
       </c>
-      <c r="B24" s="25"/>
-      <c r="C24" s="25"/>
-      <c r="D24" s="25"/>
-      <c r="E24" s="25"/>
-      <c r="F24" s="25"/>
-      <c r="G24" s="25"/>
-      <c r="H24" s="25"/>
-      <c r="I24" s="25"/>
-      <c r="J24" s="25"/>
-      <c r="K24" s="25"/>
-      <c r="L24" s="25"/>
-      <c r="M24" s="27"/>
-      <c r="N24" s="42"/>
-      <c r="O24" s="31"/>
-      <c r="P24" s="31"/>
-      <c r="Q24" s="31"/>
-      <c r="R24" s="31"/>
-      <c r="S24" s="31"/>
-      <c r="T24" s="31"/>
-      <c r="U24" s="31"/>
-      <c r="V24" s="31"/>
-      <c r="W24" s="31"/>
-      <c r="X24" s="31"/>
-      <c r="Y24" s="31"/>
-      <c r="Z24" s="31"/>
+      <c r="B24" s="26"/>
+      <c r="C24" s="26"/>
+      <c r="D24" s="26"/>
+      <c r="E24" s="26"/>
+      <c r="F24" s="26"/>
+      <c r="G24" s="26"/>
+      <c r="H24" s="26"/>
+      <c r="I24" s="26"/>
+      <c r="J24" s="26"/>
+      <c r="K24" s="26"/>
+      <c r="L24" s="26"/>
+      <c r="M24" s="28"/>
+      <c r="N24" s="43"/>
+      <c r="O24" s="32"/>
+      <c r="P24" s="32"/>
+      <c r="Q24" s="32"/>
+      <c r="R24" s="32"/>
+      <c r="S24" s="32"/>
+      <c r="T24" s="32"/>
+      <c r="U24" s="32"/>
+      <c r="V24" s="32"/>
+      <c r="W24" s="32"/>
+      <c r="X24" s="32"/>
+      <c r="Y24" s="32"/>
+      <c r="Z24" s="32"/>
       <c r="AA24" s="3"/>
     </row>
     <row r="25" spans="1:27" ht="153" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A25" s="14" t="s">
-        <v>72</v>
+        <v>74</v>
       </c>
       <c r="B25" s="15" t="s">
-        <v>73</v>
+        <v>75</v>
       </c>
       <c r="C25" s="16" t="s">
-        <v>74</v>
+        <v>76</v>
       </c>
-      <c r="D25" s="40" t="s">
-        <v>75</v>
+      <c r="D25" s="41" t="s">
+        <v>77</v>
       </c>
-      <c r="E25" s="25"/>
-      <c r="F25" s="25"/>
+      <c r="E25" s="26"/>
+      <c r="F25" s="26"/>
       <c r="G25" s="17" t="s">
-        <v>76</v>
+        <v>78</v>
       </c>
       <c r="H25" s="18">
         <v>46248</v>
@@ -1854,7 +1881,7 @@
         <v>7</v>
       </c>
       <c r="J25" s="16" t="s">
-        <v>77</v>
+        <v>79</v>
       </c>
       <c r="K25" s="18"/>
       <c r="L25" s="14"/>
@@ -1876,21 +1903,21 @@
     </row>
     <row r="26" spans="1:27" ht="174" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A26" s="14" t="s">
-        <v>78</v>
+        <v>80</v>
       </c>
       <c r="B26" s="15" t="s">
-        <v>79</v>
+        <v>81</v>
       </c>
       <c r="C26" s="16" t="s">
-        <v>80</v>
+        <v>82</v>
       </c>
-      <c r="D26" s="40" t="s">
-        <v>81</v>
+      <c r="D26" s="41" t="s">
+        <v>83</v>
       </c>
-      <c r="E26" s="25"/>
-      <c r="F26" s="25"/>
-      <c r="G26" s="24" t="s">
-        <v>82</v>
+      <c r="E26" s="26"/>
+      <c r="F26" s="26"/>
+      <c r="G26" s="25" t="s">
+        <v>84</v>
       </c>
       <c r="H26" s="18">
         <v>46248</v>
@@ -1899,11 +1926,11 @@
         <v>7</v>
       </c>
       <c r="J26" s="16" t="s">
-        <v>83</v>
+        <v>85</v>
       </c>
       <c r="K26" s="18"/>
       <c r="L26" s="14"/>
-      <c r="M26" s="22"/>
+      <c r="M26" s="23"/>
       <c r="N26" s="3"/>
       <c r="O26" s="3"/>
       <c r="P26" s="3"/>
@@ -2216,7 +2243,7 @@
       <c r="D37" s="3"/>
       <c r="E37" s="3"/>
       <c r="F37" s="3"/>
-      <c r="G37" s="21"/>
+      <c r="G37" s="22"/>
       <c r="H37" s="3"/>
       <c r="I37" s="3"/>
       <c r="J37" s="3"/>
@@ -29891,9 +29918,11 @@
     <hyperlink ref="G18" r:id="rId6" xr:uid="{00000000-0004-0000-0B00-000005000000}"/>
     <hyperlink ref="G19" r:id="rId7" xr:uid="{00000000-0004-0000-0B00-000006000000}"/>
     <hyperlink ref="G21" r:id="rId8" xr:uid="{00000000-0004-0000-0B00-000007000000}"/>
-    <hyperlink ref="G23" r:id="rId9" xr:uid="{00000000-0004-0000-0B00-000008000000}"/>
-    <hyperlink ref="G25" r:id="rId10" xr:uid="{00000000-0004-0000-0B00-000009000000}"/>
-    <hyperlink ref="G26" r:id="rId11" xr:uid="{00000000-0004-0000-0B00-00000A000000}"/>
+    <hyperlink ref="M21" r:id="rId9" xr:uid="{00000000-0004-0000-0B00-000008000000}"/>
+    <hyperlink ref="G23" r:id="rId10" xr:uid="{00000000-0004-0000-0B00-000009000000}"/>
+    <hyperlink ref="M23" r:id="rId11" xr:uid="{00000000-0004-0000-0B00-00000A000000}"/>
+    <hyperlink ref="G25" r:id="rId12" xr:uid="{00000000-0004-0000-0B00-00000B000000}"/>
+    <hyperlink ref="G26" r:id="rId13" xr:uid="{00000000-0004-0000-0B00-00000C000000}"/>
   </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>

--- a/TestCases/Notification_TestCase.xlsx
+++ b/TestCases/Notification_TestCase.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\DoAnNganh\SpringMediCareWeb-Selenium-Testing\TestCases\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D49FAF3A-CEAE-4E5D-8DF6-9C7816123175}" xr6:coauthVersionLast="36" xr6:coauthVersionMax="36" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{2B3496DE-3E6C-4506-992D-615801454139}" xr6:coauthVersionLast="36" xr6:coauthVersionMax="36" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="0" yWindow="0" windowWidth="23040" windowHeight="8940" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -400,7 +400,7 @@
   <numFmts count="1">
     <numFmt numFmtId="165" formatCode="d\-m"/>
   </numFmts>
-  <fonts count="12" x14ac:knownFonts="1">
+  <fonts count="11" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color rgb="FF000000"/>
@@ -413,6 +413,10 @@
       <name val="Tahoma"/>
     </font>
     <font>
+      <sz val="11"/>
+      <name val="MS PGothic"/>
+    </font>
+    <font>
       <b/>
       <sz val="11"/>
       <color theme="1"/>
@@ -422,10 +426,6 @@
       <sz val="11"/>
       <color theme="1"/>
       <name val="Arial"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <name val="MS PGothic"/>
     </font>
     <font>
       <b/>
@@ -448,12 +448,6 @@
       <sz val="11"/>
       <color rgb="FFFF0000"/>
       <name val="Tahoma"/>
-    </font>
-    <font>
-      <u/>
-      <sz val="11"/>
-      <color theme="1"/>
-      <name val="Arial"/>
     </font>
     <font>
       <u/>
@@ -636,12 +630,12 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="44">
+  <cellXfs count="43">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
-    <xf numFmtId="0" fontId="2" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1"/>
     <xf numFmtId="0" fontId="3" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1"/>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
-    <xf numFmtId="0" fontId="2" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="4" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="3" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
@@ -657,10 +651,10 @@
     <xf numFmtId="0" fontId="1" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="2" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1"/>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1"/>
-    <xf numFmtId="0" fontId="3" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1"/>
-    <xf numFmtId="0" fontId="3" fillId="4" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="4" fillId="2" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="4" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="4" fillId="4" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="top"/>
     </xf>
@@ -676,31 +670,28 @@
     <xf numFmtId="165" fontId="8" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="top"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1"/>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="top"/>
     </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="top"/>
     </xf>
     <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="top"/>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="10" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="3" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="4" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -716,13 +707,13 @@
     <xf numFmtId="0" fontId="5" fillId="3" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1"/>
-    <xf numFmtId="0" fontId="2" fillId="5" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="3" fillId="5" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1"/>
     <xf numFmtId="0" fontId="6" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="6" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1"/>
-    <xf numFmtId="0" fontId="2" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="3" fillId="6" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="3" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -964,9 +955,9 @@
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="31"/>
-      <c r="C1" s="32"/>
-      <c r="D1" s="32"/>
+      <c r="B1" s="30"/>
+      <c r="C1" s="31"/>
+      <c r="D1" s="31"/>
       <c r="E1" s="2"/>
       <c r="F1" s="2"/>
       <c r="G1" s="2"/>
@@ -993,9 +984,9 @@
     </row>
     <row r="2" spans="1:27" ht="13.8" x14ac:dyDescent="0.25">
       <c r="A2" s="2"/>
-      <c r="B2" s="30"/>
-      <c r="C2" s="30"/>
-      <c r="D2" s="30"/>
+      <c r="B2" s="29"/>
+      <c r="C2" s="29"/>
+      <c r="D2" s="29"/>
       <c r="E2" s="2"/>
       <c r="F2" s="2"/>
       <c r="G2" s="2"/>
@@ -1024,11 +1015,11 @@
       <c r="A3" s="4" t="s">
         <v>1</v>
       </c>
-      <c r="B3" s="33" t="s">
+      <c r="B3" s="32" t="s">
         <v>2</v>
       </c>
-      <c r="C3" s="26"/>
-      <c r="D3" s="28"/>
+      <c r="C3" s="25"/>
+      <c r="D3" s="27"/>
       <c r="E3" s="2"/>
       <c r="F3" s="2"/>
       <c r="G3" s="2"/>
@@ -1057,11 +1048,11 @@
       <c r="A4" s="4" t="s">
         <v>3</v>
       </c>
-      <c r="B4" s="34" t="s">
+      <c r="B4" s="33" t="s">
         <v>20</v>
       </c>
-      <c r="C4" s="26"/>
-      <c r="D4" s="28"/>
+      <c r="C4" s="25"/>
+      <c r="D4" s="27"/>
       <c r="E4" s="2"/>
       <c r="F4" s="2"/>
       <c r="G4" s="2"/>
@@ -1090,11 +1081,11 @@
       <c r="A5" s="4" t="s">
         <v>4</v>
       </c>
-      <c r="B5" s="33" t="s">
+      <c r="B5" s="32" t="s">
         <v>21</v>
       </c>
-      <c r="C5" s="26"/>
-      <c r="D5" s="28"/>
+      <c r="C5" s="25"/>
+      <c r="D5" s="27"/>
       <c r="E5" s="2"/>
       <c r="F5" s="2"/>
       <c r="G5" s="2"/>
@@ -1223,39 +1214,39 @@
       <c r="AA8" s="3"/>
     </row>
     <row r="9" spans="1:27" ht="13.8" x14ac:dyDescent="0.25">
-      <c r="A9" s="35" t="s">
+      <c r="A9" s="34" t="s">
         <v>9</v>
       </c>
-      <c r="B9" s="36" t="s">
+      <c r="B9" s="35" t="s">
         <v>10</v>
       </c>
-      <c r="C9" s="35" t="s">
+      <c r="C9" s="34" t="s">
         <v>11</v>
       </c>
-      <c r="D9" s="37" t="s">
+      <c r="D9" s="36" t="s">
         <v>12</v>
       </c>
-      <c r="E9" s="32"/>
-      <c r="F9" s="32"/>
-      <c r="G9" s="35" t="s">
+      <c r="E9" s="31"/>
+      <c r="F9" s="31"/>
+      <c r="G9" s="34" t="s">
         <v>13</v>
       </c>
-      <c r="H9" s="38" t="s">
+      <c r="H9" s="37" t="s">
         <v>14</v>
       </c>
-      <c r="I9" s="38" t="s">
+      <c r="I9" s="37" t="s">
         <v>15</v>
       </c>
-      <c r="J9" s="38" t="s">
+      <c r="J9" s="37" t="s">
         <v>16</v>
       </c>
-      <c r="K9" s="38" t="s">
+      <c r="K9" s="37" t="s">
         <v>17</v>
       </c>
-      <c r="L9" s="38" t="s">
+      <c r="L9" s="37" t="s">
         <v>18</v>
       </c>
-      <c r="M9" s="38" t="s">
+      <c r="M9" s="37" t="s">
         <v>19</v>
       </c>
       <c r="N9" s="3"/>
@@ -1274,19 +1265,19 @@
       <c r="AA9" s="3"/>
     </row>
     <row r="10" spans="1:27" ht="13.8" x14ac:dyDescent="0.25">
-      <c r="A10" s="27"/>
-      <c r="B10" s="27"/>
-      <c r="C10" s="27"/>
-      <c r="D10" s="29"/>
-      <c r="E10" s="30"/>
-      <c r="F10" s="30"/>
-      <c r="G10" s="27"/>
-      <c r="H10" s="27"/>
-      <c r="I10" s="27"/>
-      <c r="J10" s="27"/>
-      <c r="K10" s="27"/>
-      <c r="L10" s="27"/>
-      <c r="M10" s="27"/>
+      <c r="A10" s="26"/>
+      <c r="B10" s="26"/>
+      <c r="C10" s="26"/>
+      <c r="D10" s="28"/>
+      <c r="E10" s="29"/>
+      <c r="F10" s="29"/>
+      <c r="G10" s="26"/>
+      <c r="H10" s="26"/>
+      <c r="I10" s="26"/>
+      <c r="J10" s="26"/>
+      <c r="K10" s="26"/>
+      <c r="L10" s="26"/>
+      <c r="M10" s="26"/>
       <c r="N10" s="3"/>
       <c r="O10" s="3"/>
       <c r="P10" s="3"/>
@@ -1304,18 +1295,18 @@
     </row>
     <row r="11" spans="1:27" ht="13.8" x14ac:dyDescent="0.25">
       <c r="A11" s="13"/>
-      <c r="B11" s="39"/>
-      <c r="C11" s="26"/>
-      <c r="D11" s="26"/>
-      <c r="E11" s="26"/>
-      <c r="F11" s="26"/>
-      <c r="G11" s="26"/>
-      <c r="H11" s="26"/>
-      <c r="I11" s="26"/>
-      <c r="J11" s="26"/>
-      <c r="K11" s="26"/>
-      <c r="L11" s="26"/>
-      <c r="M11" s="26"/>
+      <c r="B11" s="38"/>
+      <c r="C11" s="25"/>
+      <c r="D11" s="25"/>
+      <c r="E11" s="25"/>
+      <c r="F11" s="25"/>
+      <c r="G11" s="25"/>
+      <c r="H11" s="25"/>
+      <c r="I11" s="25"/>
+      <c r="J11" s="25"/>
+      <c r="K11" s="25"/>
+      <c r="L11" s="25"/>
+      <c r="M11" s="25"/>
       <c r="N11" s="3"/>
       <c r="O11" s="3"/>
       <c r="P11" s="3"/>
@@ -1332,21 +1323,21 @@
       <c r="AA11" s="3"/>
     </row>
     <row r="12" spans="1:27" ht="13.8" x14ac:dyDescent="0.25">
-      <c r="A12" s="40" t="s">
+      <c r="A12" s="39" t="s">
         <v>22</v>
       </c>
-      <c r="B12" s="26"/>
-      <c r="C12" s="26"/>
-      <c r="D12" s="26"/>
-      <c r="E12" s="26"/>
-      <c r="F12" s="26"/>
-      <c r="G12" s="26"/>
-      <c r="H12" s="26"/>
-      <c r="I12" s="26"/>
-      <c r="J12" s="26"/>
-      <c r="K12" s="26"/>
-      <c r="L12" s="26"/>
-      <c r="M12" s="28"/>
+      <c r="B12" s="25"/>
+      <c r="C12" s="25"/>
+      <c r="D12" s="25"/>
+      <c r="E12" s="25"/>
+      <c r="F12" s="25"/>
+      <c r="G12" s="25"/>
+      <c r="H12" s="25"/>
+      <c r="I12" s="25"/>
+      <c r="J12" s="25"/>
+      <c r="K12" s="25"/>
+      <c r="L12" s="25"/>
+      <c r="M12" s="27"/>
       <c r="N12" s="3"/>
       <c r="O12" s="3"/>
       <c r="P12" s="3"/>
@@ -1372,11 +1363,11 @@
       <c r="C13" s="16" t="s">
         <v>25</v>
       </c>
-      <c r="D13" s="41" t="s">
+      <c r="D13" s="40" t="s">
         <v>26</v>
       </c>
-      <c r="E13" s="26"/>
-      <c r="F13" s="26"/>
+      <c r="E13" s="25"/>
+      <c r="F13" s="25"/>
       <c r="G13" s="17" t="s">
         <v>27</v>
       </c>
@@ -1417,11 +1408,11 @@
       <c r="C14" s="16" t="s">
         <v>31</v>
       </c>
-      <c r="D14" s="41" t="s">
+      <c r="D14" s="40" t="s">
         <v>32</v>
       </c>
-      <c r="E14" s="26"/>
-      <c r="F14" s="26"/>
+      <c r="E14" s="25"/>
+      <c r="F14" s="25"/>
       <c r="G14" s="17" t="s">
         <v>33</v>
       </c>
@@ -1459,21 +1450,21 @@
       <c r="AA14" s="3"/>
     </row>
     <row r="15" spans="1:27" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A15" s="40" t="s">
+      <c r="A15" s="39" t="s">
         <v>36</v>
       </c>
-      <c r="B15" s="26"/>
-      <c r="C15" s="26"/>
-      <c r="D15" s="26"/>
-      <c r="E15" s="26"/>
-      <c r="F15" s="26"/>
-      <c r="G15" s="26"/>
-      <c r="H15" s="26"/>
-      <c r="I15" s="26"/>
-      <c r="J15" s="26"/>
-      <c r="K15" s="26"/>
-      <c r="L15" s="26"/>
-      <c r="M15" s="28"/>
+      <c r="B15" s="25"/>
+      <c r="C15" s="25"/>
+      <c r="D15" s="25"/>
+      <c r="E15" s="25"/>
+      <c r="F15" s="25"/>
+      <c r="G15" s="25"/>
+      <c r="H15" s="25"/>
+      <c r="I15" s="25"/>
+      <c r="J15" s="25"/>
+      <c r="K15" s="25"/>
+      <c r="L15" s="25"/>
+      <c r="M15" s="27"/>
       <c r="N15" s="3"/>
       <c r="O15" s="3"/>
       <c r="P15" s="3"/>
@@ -1499,11 +1490,11 @@
       <c r="C16" s="16" t="s">
         <v>39</v>
       </c>
-      <c r="D16" s="41" t="s">
+      <c r="D16" s="40" t="s">
         <v>40</v>
       </c>
-      <c r="E16" s="26"/>
-      <c r="F16" s="26"/>
+      <c r="E16" s="25"/>
+      <c r="F16" s="25"/>
       <c r="G16" s="17" t="s">
         <v>41</v>
       </c>
@@ -1541,21 +1532,21 @@
       <c r="AA16" s="3"/>
     </row>
     <row r="17" spans="1:27" ht="13.8" x14ac:dyDescent="0.25">
-      <c r="A17" s="40" t="s">
+      <c r="A17" s="39" t="s">
         <v>44</v>
       </c>
-      <c r="B17" s="26"/>
-      <c r="C17" s="26"/>
-      <c r="D17" s="26"/>
-      <c r="E17" s="26"/>
-      <c r="F17" s="26"/>
-      <c r="G17" s="26"/>
-      <c r="H17" s="26"/>
-      <c r="I17" s="26"/>
-      <c r="J17" s="26"/>
-      <c r="K17" s="26"/>
-      <c r="L17" s="26"/>
-      <c r="M17" s="28"/>
+      <c r="B17" s="25"/>
+      <c r="C17" s="25"/>
+      <c r="D17" s="25"/>
+      <c r="E17" s="25"/>
+      <c r="F17" s="25"/>
+      <c r="G17" s="25"/>
+      <c r="H17" s="25"/>
+      <c r="I17" s="25"/>
+      <c r="J17" s="25"/>
+      <c r="K17" s="25"/>
+      <c r="L17" s="25"/>
+      <c r="M17" s="27"/>
       <c r="N17" s="3"/>
       <c r="O17" s="3"/>
       <c r="P17" s="3"/>
@@ -1581,11 +1572,11 @@
       <c r="C18" s="16" t="s">
         <v>47</v>
       </c>
-      <c r="D18" s="41" t="s">
+      <c r="D18" s="40" t="s">
         <v>48</v>
       </c>
-      <c r="E18" s="26"/>
-      <c r="F18" s="26"/>
+      <c r="E18" s="25"/>
+      <c r="F18" s="25"/>
       <c r="G18" s="17" t="s">
         <v>49</v>
       </c>
@@ -1626,11 +1617,11 @@
       <c r="C19" s="16" t="s">
         <v>53</v>
       </c>
-      <c r="D19" s="41" t="s">
+      <c r="D19" s="40" t="s">
         <v>54</v>
       </c>
-      <c r="E19" s="26"/>
-      <c r="F19" s="26"/>
+      <c r="E19" s="25"/>
+      <c r="F19" s="25"/>
       <c r="G19" s="17" t="s">
         <v>55</v>
       </c>
@@ -1662,21 +1653,21 @@
       <c r="AA19" s="3"/>
     </row>
     <row r="20" spans="1:27" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A20" s="40" t="s">
+      <c r="A20" s="39" t="s">
         <v>57</v>
       </c>
-      <c r="B20" s="26"/>
-      <c r="C20" s="26"/>
-      <c r="D20" s="26"/>
-      <c r="E20" s="26"/>
-      <c r="F20" s="26"/>
-      <c r="G20" s="26"/>
-      <c r="H20" s="26"/>
-      <c r="I20" s="26"/>
-      <c r="J20" s="26"/>
-      <c r="K20" s="26"/>
-      <c r="L20" s="26"/>
-      <c r="M20" s="28"/>
+      <c r="B20" s="25"/>
+      <c r="C20" s="25"/>
+      <c r="D20" s="25"/>
+      <c r="E20" s="25"/>
+      <c r="F20" s="25"/>
+      <c r="G20" s="25"/>
+      <c r="H20" s="25"/>
+      <c r="I20" s="25"/>
+      <c r="J20" s="25"/>
+      <c r="K20" s="25"/>
+      <c r="L20" s="25"/>
+      <c r="M20" s="27"/>
       <c r="N20" s="3"/>
       <c r="O20" s="3"/>
       <c r="P20" s="3"/>
@@ -1702,11 +1693,11 @@
       <c r="C21" s="16" t="s">
         <v>60</v>
       </c>
-      <c r="D21" s="41" t="s">
+      <c r="D21" s="40" t="s">
         <v>61</v>
       </c>
-      <c r="E21" s="26"/>
-      <c r="F21" s="26"/>
+      <c r="E21" s="25"/>
+      <c r="F21" s="25"/>
       <c r="G21" s="17" t="s">
         <v>62</v>
       </c>
@@ -1744,34 +1735,34 @@
       <c r="AA21" s="3"/>
     </row>
     <row r="22" spans="1:27" ht="13.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A22" s="40" t="s">
+      <c r="A22" s="39" t="s">
         <v>65</v>
       </c>
-      <c r="B22" s="26"/>
-      <c r="C22" s="26"/>
-      <c r="D22" s="26"/>
-      <c r="E22" s="26"/>
-      <c r="F22" s="26"/>
-      <c r="G22" s="26"/>
-      <c r="H22" s="26"/>
-      <c r="I22" s="26"/>
-      <c r="J22" s="26"/>
-      <c r="K22" s="26"/>
-      <c r="L22" s="26"/>
-      <c r="M22" s="28"/>
-      <c r="N22" s="42"/>
-      <c r="O22" s="32"/>
-      <c r="P22" s="32"/>
-      <c r="Q22" s="32"/>
-      <c r="R22" s="32"/>
-      <c r="S22" s="32"/>
-      <c r="T22" s="32"/>
-      <c r="U22" s="32"/>
-      <c r="V22" s="32"/>
-      <c r="W22" s="32"/>
-      <c r="X22" s="32"/>
-      <c r="Y22" s="32"/>
-      <c r="Z22" s="32"/>
+      <c r="B22" s="25"/>
+      <c r="C22" s="25"/>
+      <c r="D22" s="25"/>
+      <c r="E22" s="25"/>
+      <c r="F22" s="25"/>
+      <c r="G22" s="25"/>
+      <c r="H22" s="25"/>
+      <c r="I22" s="25"/>
+      <c r="J22" s="25"/>
+      <c r="K22" s="25"/>
+      <c r="L22" s="25"/>
+      <c r="M22" s="27"/>
+      <c r="N22" s="41"/>
+      <c r="O22" s="31"/>
+      <c r="P22" s="31"/>
+      <c r="Q22" s="31"/>
+      <c r="R22" s="31"/>
+      <c r="S22" s="31"/>
+      <c r="T22" s="31"/>
+      <c r="U22" s="31"/>
+      <c r="V22" s="31"/>
+      <c r="W22" s="31"/>
+      <c r="X22" s="31"/>
+      <c r="Y22" s="31"/>
+      <c r="Z22" s="31"/>
       <c r="AA22" s="3"/>
     </row>
     <row r="23" spans="1:27" ht="155.25" customHeight="1" x14ac:dyDescent="0.25">
@@ -1784,12 +1775,12 @@
       <c r="C23" s="16" t="s">
         <v>68</v>
       </c>
-      <c r="D23" s="41" t="s">
+      <c r="D23" s="40" t="s">
         <v>69</v>
       </c>
-      <c r="E23" s="26"/>
-      <c r="F23" s="26"/>
-      <c r="G23" s="24" t="s">
+      <c r="E23" s="25"/>
+      <c r="F23" s="25"/>
+      <c r="G23" s="23" t="s">
         <v>70</v>
       </c>
       <c r="H23" s="18">
@@ -1807,7 +1798,7 @@
       <c r="L23" s="14" t="s">
         <v>5</v>
       </c>
-      <c r="M23" s="21" t="s">
+      <c r="M23" s="17" t="s">
         <v>72</v>
       </c>
       <c r="N23" s="3"/>
@@ -1826,34 +1817,34 @@
       <c r="AA23" s="3"/>
     </row>
     <row r="24" spans="1:27" ht="13.8" x14ac:dyDescent="0.25">
-      <c r="A24" s="40" t="s">
+      <c r="A24" s="39" t="s">
         <v>73</v>
       </c>
-      <c r="B24" s="26"/>
-      <c r="C24" s="26"/>
-      <c r="D24" s="26"/>
-      <c r="E24" s="26"/>
-      <c r="F24" s="26"/>
-      <c r="G24" s="26"/>
-      <c r="H24" s="26"/>
-      <c r="I24" s="26"/>
-      <c r="J24" s="26"/>
-      <c r="K24" s="26"/>
-      <c r="L24" s="26"/>
-      <c r="M24" s="28"/>
-      <c r="N24" s="43"/>
-      <c r="O24" s="32"/>
-      <c r="P24" s="32"/>
-      <c r="Q24" s="32"/>
-      <c r="R24" s="32"/>
-      <c r="S24" s="32"/>
-      <c r="T24" s="32"/>
-      <c r="U24" s="32"/>
-      <c r="V24" s="32"/>
-      <c r="W24" s="32"/>
-      <c r="X24" s="32"/>
-      <c r="Y24" s="32"/>
-      <c r="Z24" s="32"/>
+      <c r="B24" s="25"/>
+      <c r="C24" s="25"/>
+      <c r="D24" s="25"/>
+      <c r="E24" s="25"/>
+      <c r="F24" s="25"/>
+      <c r="G24" s="25"/>
+      <c r="H24" s="25"/>
+      <c r="I24" s="25"/>
+      <c r="J24" s="25"/>
+      <c r="K24" s="25"/>
+      <c r="L24" s="25"/>
+      <c r="M24" s="27"/>
+      <c r="N24" s="42"/>
+      <c r="O24" s="31"/>
+      <c r="P24" s="31"/>
+      <c r="Q24" s="31"/>
+      <c r="R24" s="31"/>
+      <c r="S24" s="31"/>
+      <c r="T24" s="31"/>
+      <c r="U24" s="31"/>
+      <c r="V24" s="31"/>
+      <c r="W24" s="31"/>
+      <c r="X24" s="31"/>
+      <c r="Y24" s="31"/>
+      <c r="Z24" s="31"/>
       <c r="AA24" s="3"/>
     </row>
     <row r="25" spans="1:27" ht="153" customHeight="1" x14ac:dyDescent="0.25">
@@ -1866,11 +1857,11 @@
       <c r="C25" s="16" t="s">
         <v>76</v>
       </c>
-      <c r="D25" s="41" t="s">
+      <c r="D25" s="40" t="s">
         <v>77</v>
       </c>
-      <c r="E25" s="26"/>
-      <c r="F25" s="26"/>
+      <c r="E25" s="25"/>
+      <c r="F25" s="25"/>
       <c r="G25" s="17" t="s">
         <v>78</v>
       </c>
@@ -1911,12 +1902,12 @@
       <c r="C26" s="16" t="s">
         <v>82</v>
       </c>
-      <c r="D26" s="41" t="s">
+      <c r="D26" s="40" t="s">
         <v>83</v>
       </c>
-      <c r="E26" s="26"/>
-      <c r="F26" s="26"/>
-      <c r="G26" s="25" t="s">
+      <c r="E26" s="25"/>
+      <c r="F26" s="25"/>
+      <c r="G26" s="24" t="s">
         <v>84</v>
       </c>
       <c r="H26" s="18">
@@ -1930,7 +1921,7 @@
       </c>
       <c r="K26" s="18"/>
       <c r="L26" s="14"/>
-      <c r="M26" s="23"/>
+      <c r="M26" s="21"/>
       <c r="N26" s="3"/>
       <c r="O26" s="3"/>
       <c r="P26" s="3"/>

--- a/TestCases/Notification_TestCase.xlsx
+++ b/TestCases/Notification_TestCase.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\DoAnNganh\SpringMediCareWeb-Selenium-Testing\TestCases\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{2B3496DE-3E6C-4506-992D-615801454139}" xr6:coauthVersionLast="36" xr6:coauthVersionMax="36" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{3DC75F31-9DF2-41BC-B63B-EC80D623A3AD}" xr6:coauthVersionLast="36" xr6:coauthVersionMax="36" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="0" windowWidth="23040" windowHeight="8940" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="0" yWindow="0" windowWidth="12012" windowHeight="6960" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="NOTIFICATION" sheetId="12" r:id="rId1"/>
@@ -100,20 +100,21 @@
     <t>Kiểm tra Patient nhận được thông báo đúng sau khi Admin xác nhận lịch hẹn mà Patient đã đặt.</t>
   </si>
   <si>
-    <t>1: Patient thực hiện đặt một lịch khám hợp lệ.
+    <t xml:space="preserve">1: Patient thực hiện đặt một lịch khám hợp lệ.
 2: Đăng nhập bằng Admin.
 3: Mở Quản lý lịch hẹn và xác nhận lịch vừa tạo.
 4: Đăng xuất Admin và đăng nhập lại bằng Patient.
 5: Mở trang Thông báo.
 6: Tìm thông báo liên quan đến lịch hẹn vừa được xác nhận.
-7: Kiểm tra loại, nội dung và thời gian của thông báo.</t>
+7: Kiểm tra loại, nội dung và thời gian của thông báo.
+</t>
   </si>
   <si>
-    <t>Patient nhận được thông báo liên quan đến lịch hẹn vừa được xác nhận.
-Thông báo thuộc đúng loại Lịch hẹn.
-Nội dung thông báo tương ứng đúng với lịch của Patient.
-Không hiển thị thông báo của một lịch hẹn khác.
-Thời gian thông báo được ghi nhận và hiển thị.</t>
+    <t>Patient nhận được thông báo cho đúng lịch hẹn vừa được Admin xác nhận.
+Thông báo thuộc loại [Lịch hẹn].
+Nội dung thông báo chứa đúng mã lịch hẹn và thể hiện lịch hẹn đã được xác nhận.
+Không lấy nhầm thông báo của lịch hẹn khác.
+Thời gian thông báo được hiển thị và đúng định dạng HH:mm:ss dd/MM/yyyy.</t>
   </si>
   <si>
     <t>TCNotification1_1, TCNotification1_2, TCNotification1_3</t>
@@ -137,11 +138,11 @@
 7: Kiểm tra loại và nội dung thông báo.</t>
   </si>
   <si>
-    <t>Patient nhận được thông báo về việc lịch hẹn bị hủy.
-Thông báo thuộc đúng loại Lịch hẹn.
-Nội dung thông báo tương ứng với lịch hẹn vừa bị xử lý.
-Không hiển thị nhầm thông tin của lịch hẹn khác.
-Thông báo chỉ xuất hiện trong tài khoản Patient sở hữu lịch hẹn.</t>
+    <t>Patient nhận được thông báo cho đúng lịch hẹn vừa bị Admin hủy.
+Thông báo thuộc loại [Lịch hẹn].
+Nội dung thông báo chứa đúng mã lịch hẹn và thể hiện lịch hẹn đã bị hủy.
+Không lấy nhầm thông báo của lịch hẹn khác.
+Thời gian thông báo được hiển thị và đúng định dạng HH:mm:ss dd/MM/yyyy.</t>
   </si>
   <si>
     <t>TCNotification2_1 TCNotification2_2, TCNotification2_3</t>
@@ -169,14 +170,10 @@
 5: Lưu hồ sơ bệnh án.
 6: Đăng xuất Doctor và đăng nhập lại bằng Patient.
 7: Mở trang Thông báo.
-8: Kiểm tra thông báo liên quan đến kết quả khám vừa được Doctor lưu.</t>
+8: Tìm và kiểm tra thông báo mới phát sinh sau khi Doctor lưu hồ sơ bệnh án, bao gồm nội dung và thời gian thông báo.</t>
   </si>
   <si>
-    <t>Doctor lưu kết quả khám thành công.
-Patient nhận được thông báo mới sau khi kết quả khám được ghi nhận.
-Nội dung thông báo liên quan đúng đến lần khám của Patient.
-Thông báo không được gửi nhầm sang Patient khác.
-Thời gian thông báo được hiển thị.</t>
+    <t>Patient nhận được thông báo mới sau khi Doctor cập nhật kết quả khám. Loại thông báo hiển thị là [Thông báo], nội dung thể hiện “Kết quả khám của bạn đã được bác sĩ ... cập nhật”, kèm thời gian thông báo.</t>
   </si>
   <si>
     <t>TCNotification3_1, TCNotification3_2, TCNotification3_3</t>
@@ -197,21 +194,19 @@
     <t>Kiểm tra khi Patient phát sinh nhiều thông báo từ các sự kiện khác nhau, các thông báo được lưu thành các bản ghi riêng biệt và không ghi đè lẫn nhau.</t>
   </si>
   <si>
-    <t>1: Chuẩn bị Patient đã có ít nhất một thông báo trong trang Thông báo.
-2: Thực hiện thêm một sự kiện có phát sinh thông báo mới cho Patient.
-3: Đăng nhập bằng Patient.
-4: Mở trang Thông báo.
-5: Tìm thông báo mới vừa phát sinh.
-6: Kiểm tra các thông báo đã tồn tại trước đó.
-7: Đối chiếu loại, nội dung và thời gian của các thông báo.</t>
+    <t>1: Patient đã có ít nhất một thông báo trước đó.
+2: Patient tạo thêm một lịch hẹn mới.
+3: Admin xác nhận lịch hẹn mới.
+4: Đăng nhập lại bằng Patient.
+5: Mở trang Thông báo.
+6: Kiểm tra thông báo mới của lịch vừa được xác nhận.
+7: Kiểm tra thông báo cũ vẫn còn hiển thị.</t>
   </si>
   <si>
-    <t>Thông báo mới được thêm vào danh sách.
-Các thông báo cũ vẫn được giữ nguyên.
-Mỗi sự kiện được hiển thị thành một thông báo riêng biệt.
-Thông báo mới không ghi đè nội dung của thông báo cũ.
-Loại, nội dung và thời gian của từng thông báo được hiển thị đúng.
-Không phát sinh bản ghi trùng ngoài mong đợi.</t>
+    <t>Patient nhận được thông báo mới tương ứng với sự kiện vừa phát sinh.
+Thông báo mới được hiển thị trong danh sách Thông báo.
+Các thông báo đã tồn tại trước đó vẫn còn hiển thị, không bị mất hoặc ghi đè.
+Nội dung của các thông báo không bị trộn lẫn.</t>
   </si>
   <si>
     <t>TCNotification4</t>
@@ -223,24 +218,22 @@
     <t>TC-NOTIFICATION-005</t>
   </si>
   <si>
-    <t>Kiểm tra mỗi Patient chỉ xem được các thông báo thuộc tài khoản của mình và không nhìn thấy thông báo của Patient khác.</t>
+    <t>Kiểm tra thông báo được phân tách đúng giữa các tài khoản Patient, Patient này không xem được thông báo của Patient khác.</t>
   </si>
   <si>
-    <t>1: Chuẩn bị Patient A có ít nhất một thông báo xác định.
-2: Chuẩn bị Patient B có ít nhất một thông báo khác.
-3: Đăng nhập bằng Patient A.
-4: Mở trang Thông báo và ghi nhận các thông báo đang hiển thị.
-5: Đăng xuất Patient A.
-6: Đăng nhập bằng Patient B.
+    <t>1: Chuẩn bị hai tài khoản Patient A và Patient B.
+2: Tạo một sự kiện phát sinh thông báo riêng cho Patient A và ghi nhận thông tin nhận diện của thông báo A.
+3: Tạo một sự kiện phát sinh thông báo riêng cho Patient B và ghi nhận thông tin nhận diện của thông báo B.
+4: Đăng nhập Patient A và mở trang Thông báo.
+5: Kiểm tra Patient A thấy thông báo A và không thấy thông báo B.
+6: Đăng xuất Patient A, đăng nhập Patient B.
 7: Mở trang Thông báo.
-8: So sánh danh sách thông báo của hai Patient.</t>
+8: Kiểm tra Patient B thấy thông báo B và không thấy thông báo A.</t>
   </si>
   <si>
-    <t>Patient A chỉ nhìn thấy các thông báo thuộc Patient A.
-Patient B chỉ nhìn thấy các thông báo thuộc Patient B.
-Không xuất hiện thông báo của Patient A trong tài khoản Patient B và ngược lại.
-Nội dung thông báo không bị lẫn giữa hai Patient.
-Dữ liệu thông báo được phân tách đúng theo từng tài khoản.</t>
+    <t>Patient A chỉ xem được thông báo liên quan đến lịch hẹn của Patient A và không xem được thông báo của Patient B.
+Patient B chỉ xem được thông báo liên quan đến lịch hẹn của Patient B và không xem được thông báo của Patient A.
+Nội dung thông báo của hai Patient được phân tách chính xác, không xảy ra hiển thị chéo dữ liệu giữa các tài khoản.</t>
   </si>
   <si>
     <t>TCNotification5_1, TCNotification5_2</t>
@@ -259,23 +252,21 @@
     <t>Kiểm tra Patient nhận được thông báo đúng sau khi Doctor tạo và lưu đơn thuốc mới cho hồ sơ khám của Patient.</t>
   </si>
   <si>
-    <t>1: Chuẩn bị Patient có hồ sơ bệnh án đã được Doctor tạo sau khi khám.
-2: Đăng nhập bằng Doctor phụ trách hồ sơ bệnh án.
-3: Mở Chi tiết hồ sơ bệnh án của Patient.
-4: Chuyển đến phần Đơn thuốc.
-5: Chọn thuốc và nhập đầy đủ số lượng, liều dùng hợp lệ.
-6: Thực hiện Lưu đơn thuốc.
-7: Đăng xuất Doctor và đăng nhập lại bằng Patient.
-8: Mở trang Thông báo.
-9: Tìm và kiểm tra thông báo liên quan đến đơn thuốc vừa được tạo.</t>
+    <t>1: Chuẩn bị Patient có lịch hẹn đã được xác nhận.
+2: Doctor đăng nhập.
+3: Doctor mở lịch hẹn của Patient.
+4: Thực hiện khám bệnh.
+5: Nhập/lưu thông tin khám cần thiết.
+6: Mở chức năng kê đơn thuốc.
+7: Tạo đơn thuốc hợp lệ cho Patient.
+8: Đăng xuất Doctor và đăng nhập Patient.
+9: Mở Thông báo và kiểm tra notification về đơn thuốc.</t>
   </si>
   <si>
-    <t>Doctor tạo và lưu đơn thuốc thành công.
-Patient nhận được một thông báo mới sau khi đơn thuốc được tạo.
-Thông báo thuộc đúng loại [Đơn thuốc].
-Nội dung thông báo liên quan đúng đến đơn thuốc/lần khám của Patient.
-Thông báo được gửi đúng Patient sở hữu hồ sơ.
-Không gửi nhầm thông báo sang Patient khác.
+    <t>Doctor tạo đơn thuốc cho Patient thành công.
+Patient nhận được thông báo mới sau khi đơn thuốc được tạo.
+Thông báo thuộc loại [Đơn thuốc].
+Nội dung thông báo thể hiện đúng sự kiện đơn thuốc mới được tạo cho Patient.
 Thời gian thông báo được ghi nhận và hiển thị.</t>
   </si>
   <si>
@@ -306,15 +297,13 @@
 6: Lưu kết quả xét nghiệm.
 7: Đăng xuất Doctor và đăng nhập lại bằng Patient.
 8: Mở trang Thông báo.
-9: Tìm và kiểm tra thông báo liên quan đến kết quả xét nghiệm vừa được thêm.</t>
+9: Tìm thông báo mới phát sinh liên quan đến kết quả xét nghiệm vừa được lưu.</t>
   </si>
   <si>
-    <t>Kết quả xét nghiệm được lưu thành công vào đúng hồ sơ bệnh án.
-Patient nhận được một thông báo mới sau khi kết quả xét nghiệm được ghi nhận.
-Thông báo thuộc đúng loại [Kết quả xét nghiệm].
-Nội dung thông báo liên quan đúng đến kết quả xét nghiệm/hồ sơ của Patient.
-Không gửi thông báo sang Patient khác.
-Các thông báo đã có trước đó vẫn được giữ nguyên.
+    <t>Kết quả xét nghiệm được lưu thành công.
+Patient nhận được một thông báo mới sau khi kết quả xét nghiệm được cập nhật.
+Thông báo thuộc loại [Kết quả xét nghiệm].
+Nội dung thông báo thể hiện đúng sự kiện kết quả xét nghiệm của Patient đã được cập nhật.
 Thời gian thông báo được ghi nhận và hiển thị.</t>
   </si>
   <si>
@@ -344,15 +333,15 @@
 6: Kê lại đơn thuốc với thuốc, số lượng hoặc liều dùng khác.
 7: Lưu đơn thuốc mới.
 8: Đăng nhập lại bằng Patient.
-9: Mở trang Thông báo và kiểm tra thông báo mới.</t>
+9: Tìm và kiểm tra notification mới phát sinh từ đơn thuốc mới.</t>
   </si>
   <si>
-    <t>Đơn thuốc cũ được xóa theo đúng thao tác.
-Doctor kê và lưu được đơn thuốc mới.
-Patient nhận được một notification [Đơn thuốc] mới.
-Notification thể hiện Patient có đơn thuốc mới, không cần ghi “đơn thuốc đã được cập nhật”.
-Notification thuộc đúng Patient/hồ sơ.
-Các notification cũ vẫn được giữ nguyên.</t>
+    <t>Đơn thuốc cũ được xóa và đơn thuốc mới được tạo thành công.
+Patient nhận được một thông báo mới sau khi đơn thuốc mới được lưu.
+Thông báo mới thuộc loại [Đơn thuốc].
+Nội dung thông báo tương ứng với sự kiện tạo đơn thuốc mới.
+Thông báo đơn thuốc mới không bị nhầm với notification của đơn thuốc cũ.
+Thời gian thông báo được ghi nhận và hiển thị.</t>
   </si>
   <si>
     <t>TCNotification8_1, TCNotification8_2, TCNotification8_3, TCNotification8_4</t>
@@ -367,24 +356,21 @@
     <t>Kiểm tra Patient nhận được thông báo mới sau khi Doctor chỉnh sửa Chẩn đoán và Hướng điều trị của một hồ sơ bệnh án đã tồn tại.</t>
   </si>
   <si>
-    <t>1: Chuẩn bị Patient đã có hồ sơ bệnh án với Chẩn đoán và Hướng điều trị xác định.
-2: Ghi nhận Chẩn đoán và Hướng điều trị hiện tại của hồ sơ.
-3: Đăng nhập bằng Doctor phụ trách hồ sơ bệnh án.
-4: Mở Chi tiết hồ sơ bệnh án tương ứng.
-5: Chọn chức năng cập nhật hồ sơ.
-6: Thay đổi Chẩn đoán và Hướng điều trị bằng dữ liệu hợp lệ khác dữ liệu cũ.
-7: Lưu thay đổi.
-8: Đăng xuất Doctor và đăng nhập lại bằng Patient.
-9: Mở trang Thông báo và kiểm tra thông báo mới.</t>
+    <t>1: Chuẩn bị Patient đã có hồ sơ khám với Chẩn đoán và Hướng điều trị được lưu trước đó.
+2: Đăng nhập Doctor phụ trách.
+3: Mở hồ sơ khám của Patient.
+4: Chỉnh sửa Chẩn đoán và/hoặc Hướng điều trị.
+5: Lưu thông tin đã cập nhật.
+6: Đăng xuất Doctor và đăng nhập Patient.
+7: Mở trang Thông báo.
+8: Tìm và kiểm tra thông báo mới phát sinh sau khi Doctor cập nhật hồ sơ khám.</t>
   </si>
   <si>
-    <t>Doctor cập nhật Chẩn đoán và Hướng điều trị thành công.
-Dữ liệu mới được lưu vào đúng hồ sơ bệnh án đã tồn tại.
-Không tạo thêm hồ sơ bệnh án mới.
-Patient nhận được một thông báo mới sau khi hồ sơ được cập nhật.
-Nội dung thông báo liên quan đúng đến kết quả khám/hồ sơ vừa được cập nhật.
-Thông báo được gửi đúng Patient sở hữu hồ sơ.
-Các thông báo cũ vẫn được giữ nguyên.</t>
+    <t>Thông tin Chẩn đoán/Hướng điều trị được cập nhật thành công.
+Patient nhận được một thông báo mới sau khi Doctor cập nhật hồ sơ khám.
+Nội dung thông báo thể hiện đúng sự kiện hồ sơ/kết quả khám của Patient vừa được cập nhật.
+Thông báo mới không bị nhầm với thông báo đã phát sinh khi lưu kết quả khám trước đó.
+Thời gian thông báo được ghi nhận và hiển thị.</t>
   </si>
   <si>
     <t xml:space="preserve">TCNotification9_1, TCNotification9_2, TCNotification9_3, </t>
@@ -413,10 +399,6 @@
       <name val="Tahoma"/>
     </font>
     <font>
-      <sz val="11"/>
-      <name val="MS PGothic"/>
-    </font>
-    <font>
       <b/>
       <sz val="11"/>
       <color theme="1"/>
@@ -426,6 +408,10 @@
       <sz val="11"/>
       <color theme="1"/>
       <name val="Arial"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="MS PGothic"/>
     </font>
     <font>
       <b/>
@@ -632,10 +618,10 @@
   </cellStyleXfs>
   <cellXfs count="43">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1"/>
     <xf numFmtId="0" fontId="3" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1"/>
-    <xf numFmtId="0" fontId="4" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1"/>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
-    <xf numFmtId="0" fontId="3" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
@@ -651,10 +637,10 @@
     <xf numFmtId="0" fontId="1" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="2" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1"/>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1"/>
-    <xf numFmtId="0" fontId="4" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1"/>
-    <xf numFmtId="0" fontId="4" fillId="4" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="3" fillId="2" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="3" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="3" fillId="4" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="top"/>
     </xf>
@@ -670,11 +656,11 @@
     <xf numFmtId="165" fontId="8" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="top"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1"/>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="top"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="top"/>
     </xf>
     <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
@@ -686,12 +672,12 @@
     <xf numFmtId="0" fontId="10" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="4" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="3" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -707,13 +693,13 @@
     <xf numFmtId="0" fontId="5" fillId="3" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1"/>
-    <xf numFmtId="0" fontId="3" fillId="5" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="2" fillId="5" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1"/>
     <xf numFmtId="0" fontId="6" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="6" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1"/>
-    <xf numFmtId="0" fontId="3" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="2" fillId="6" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -1480,7 +1466,7 @@
       <c r="Z15" s="3"/>
       <c r="AA15" s="3"/>
     </row>
-    <row r="16" spans="1:27" ht="144" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="16" spans="1:27" ht="152.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A16" s="14" t="s">
         <v>37</v>
       </c>
@@ -1607,7 +1593,7 @@
       <c r="Z18" s="3"/>
       <c r="AA18" s="3"/>
     </row>
-    <row r="19" spans="1:27" ht="157.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="19" spans="1:27" ht="192.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A19" s="14" t="s">
         <v>51</v>
       </c>
@@ -1847,7 +1833,7 @@
       <c r="Z24" s="31"/>
       <c r="AA24" s="3"/>
     </row>
-    <row r="25" spans="1:27" ht="153" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="25" spans="1:27" ht="165" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A25" s="14" t="s">
         <v>74</v>
       </c>

--- a/TestCases/Notification_TestCase.xlsx
+++ b/TestCases/Notification_TestCase.xlsx
@@ -8,12 +8,13 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\DoAnNganh\SpringMediCareWeb-Selenium-Testing\TestCases\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{3DC75F31-9DF2-41BC-B63B-EC80D623A3AD}" xr6:coauthVersionLast="36" xr6:coauthVersionMax="36" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D1BD39C7-C933-4C0F-987A-FEA465679220}" xr6:coauthVersionLast="36" xr6:coauthVersionMax="36" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="0" yWindow="0" windowWidth="12012" windowHeight="6960" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="NOTIFICATION" sheetId="12" r:id="rId1"/>
+    <sheet name="AUTOMATION_DATA" sheetId="13" r:id="rId2"/>
   </sheets>
   <definedNames>
     <definedName name="ACTION">#REF!</definedName>
@@ -23,7 +24,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="99" uniqueCount="86">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="126" uniqueCount="103">
   <si>
     <t>TEST CASE</t>
   </si>
@@ -194,15 +195,6 @@
     <t>Kiểm tra khi Patient phát sinh nhiều thông báo từ các sự kiện khác nhau, các thông báo được lưu thành các bản ghi riêng biệt và không ghi đè lẫn nhau.</t>
   </si>
   <si>
-    <t>1: Patient đã có ít nhất một thông báo trước đó.
-2: Patient tạo thêm một lịch hẹn mới.
-3: Admin xác nhận lịch hẹn mới.
-4: Đăng nhập lại bằng Patient.
-5: Mở trang Thông báo.
-6: Kiểm tra thông báo mới của lịch vừa được xác nhận.
-7: Kiểm tra thông báo cũ vẫn còn hiển thị.</t>
-  </si>
-  <si>
     <t>Patient nhận được thông báo mới tương ứng với sự kiện vừa phát sinh.
 Thông báo mới được hiển thị trong danh sách Thông báo.
 Các thông báo đã tồn tại trước đó vẫn còn hiển thị, không bị mất hoặc ghi đè.
@@ -219,16 +211,6 @@
   </si>
   <si>
     <t>Kiểm tra thông báo được phân tách đúng giữa các tài khoản Patient, Patient này không xem được thông báo của Patient khác.</t>
-  </si>
-  <si>
-    <t>1: Chuẩn bị hai tài khoản Patient A và Patient B.
-2: Tạo một sự kiện phát sinh thông báo riêng cho Patient A và ghi nhận thông tin nhận diện của thông báo A.
-3: Tạo một sự kiện phát sinh thông báo riêng cho Patient B và ghi nhận thông tin nhận diện của thông báo B.
-4: Đăng nhập Patient A và mở trang Thông báo.
-5: Kiểm tra Patient A thấy thông báo A và không thấy thông báo B.
-6: Đăng xuất Patient A, đăng nhập Patient B.
-7: Mở trang Thông báo.
-8: Kiểm tra Patient B thấy thông báo B và không thấy thông báo A.</t>
   </si>
   <si>
     <t>Patient A chỉ xem được thông báo liên quan đến lịch hẹn của Patient A và không xem được thông báo của Patient B.
@@ -322,34 +304,6 @@
     <t>TC-NOTIFICATION-008</t>
   </si>
   <si>
-    <t>Kiểm tra Patient nhận được thông báo đơn thuốc mới sau khi Doctor xóa đơn thuốc cũ và kê lại một đơn thuốc khác cho Patient.</t>
-  </si>
-  <si>
-    <t>1: Chuẩn bị Patient đã có một đơn thuốc được lưu trước đó.
-2: Ghi nhận thông tin đơn thuốc hiện tại.
-3: Đăng nhập bằng Doctor phụ trách hồ sơ.
-4: Mở phần Đơn thuốc của hồ sơ.
-5: Xóa đơn/thuốc cũ theo chức năng hệ thống.
-6: Kê lại đơn thuốc với thuốc, số lượng hoặc liều dùng khác.
-7: Lưu đơn thuốc mới.
-8: Đăng nhập lại bằng Patient.
-9: Tìm và kiểm tra notification mới phát sinh từ đơn thuốc mới.</t>
-  </si>
-  <si>
-    <t>Đơn thuốc cũ được xóa và đơn thuốc mới được tạo thành công.
-Patient nhận được một thông báo mới sau khi đơn thuốc mới được lưu.
-Thông báo mới thuộc loại [Đơn thuốc].
-Nội dung thông báo tương ứng với sự kiện tạo đơn thuốc mới.
-Thông báo đơn thuốc mới không bị nhầm với notification của đơn thuốc cũ.
-Thời gian thông báo được ghi nhận và hiển thị.</t>
-  </si>
-  <si>
-    <t>TCNotification8_1, TCNotification8_2, TCNotification8_3, TCNotification8_4</t>
-  </si>
-  <si>
-    <t>Không phát sinh thông báo [Đơn thuốc] cho Patient sau khi Doctor xóa đơn thuốc cũ và kê lại đơn mới.</t>
-  </si>
-  <si>
     <t>TC-NOTIFICATION-009</t>
   </si>
   <si>
@@ -378,15 +332,106 @@
   <si>
     <t>Không phát sinh thông báo mới cho Patient sau khi Doctor cập nhật Chẩn đoán và Hướng điều trị của hồ sơ bệnh án.</t>
   </si>
+  <si>
+    <t>test_case_id</t>
+  </si>
+  <si>
+    <t>patient_password</t>
+  </si>
+  <si>
+    <t>notification_type</t>
+  </si>
+  <si>
+    <t>expected_keyword</t>
+  </si>
+  <si>
+    <t>patient_username</t>
+  </si>
+  <si>
+    <t>patient_an</t>
+  </si>
+  <si>
+    <t>Abc@123</t>
+  </si>
+  <si>
+    <t>[Lịch hẹn]</t>
+  </si>
+  <si>
+    <t>da duoc xac nhan</t>
+  </si>
+  <si>
+    <t>admin_username</t>
+  </si>
+  <si>
+    <t>admin_password</t>
+  </si>
+  <si>
+    <t>doctor_id</t>
+  </si>
+  <si>
+    <t>time_format</t>
+  </si>
+  <si>
+    <t>note_prefix</t>
+  </si>
+  <si>
+    <t>SELENIUM-TC-NOTIFICATION-001-</t>
+  </si>
+  <si>
+    <t>%H:%M:%S %d/%m/%Y</t>
+  </si>
+  <si>
+    <t>admin_system</t>
+  </si>
+  <si>
+    <t>1: Đăng nhập bằng Patient.
+2: Tạo một lịch hẹn mới hợp lệ.
+3: Đăng xuất Patient và đăng nhập bằng Admin.
+4: Mở trang Quản lý lịch hẹn và xác nhận lịch hẹn vừa tạo.
+5: Đăng xuất Admin và đăng nhập lại bằng Patient.
+6: Mở trang Thông báo.
+7: Kiểm tra thông báo mới của lịch vừa được xác nhận.
+8: Kiểm tra thông báo đã tồn tại trước đó vẫn còn hiển thị.</t>
+  </si>
+  <si>
+    <t>1: Đăng nhập bằng tài khoản patient_an.
+2: Mở trang Thông báo và ghi nhận danh sách thông báo đang hiển thị.
+3: Đăng xuất patient_an, sau đó đăng nhập bằng tài khoản patient_thu.
+4: Mở trang Thông báo và ghi nhận danh sách thông báo đang hiển thị.
+5: So sánh nội dung thông báo của hai Patient, xác nhận danh sách thông báo được hiển thị riêng theo từng tài khoản và không giống hoàn toàn nhau.</t>
+  </si>
+  <si>
+    <t>Kiểm tra Patient nhận được thông báo mới khi Doctor kê thêm một đơn thuốc mới cho Patient đã có đơn thuốc trước đó.</t>
+  </si>
+  <si>
+    <t>1: Chuẩn bị Patient đã có một đơn thuốc cũ.
+2: Ghi nhận notification của đơn thuốc cũ.
+3: Doctor đăng nhập.
+4: Mở hồ sơ bệnh án → tab Đơn thuốc.
+5: Kê thêm một đơn thuốc mới với thuốc/số lượng/liều dùng khác.
+6: Lưu đơn thuốc mới.
+7: Đăng xuất Doctor → đăng nhập Patient.
+8: Mở Thông báo.
+9: Tìm và kiểm tra thông báo mới phát sinh từ đơn thuốc vừa được lưu.</t>
+  </si>
+  <si>
+    <t>Đơn thuốc mới được lưu thành công. Patient nhận được một thông báo mới thuộc loại [Đơn thuốc]. Nội dung thông báo tương ứng với đơn thuốc mới vừa được tạo. Thông báo mới không bị nhầm hoặc ghi đè bởi thông báo của đơn thuốc trước đó. Thời gian thông báo được ghi nhận và hiển thị.</t>
+  </si>
+  <si>
+    <t>TCNotification8_1, TCNotification8_2, TCNotification8_3</t>
+  </si>
+  <si>
+    <t>Phát sinh đúng thông báo [Đơn thuốc] mới sau khi Doctor kê thêm đơn thuốc mới; thông báo cũ và mới được hiển thị riêng biệt.</t>
+  </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
   <numFmts count="1">
-    <numFmt numFmtId="165" formatCode="d\-m"/>
+    <numFmt numFmtId="164" formatCode="d\-m"/>
   </numFmts>
-  <fonts count="11" x14ac:knownFonts="1">
+  <fonts count="15" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color rgb="FF000000"/>
@@ -442,13 +487,39 @@
       <name val="Tahoma"/>
     </font>
     <font>
+      <sz val="11"/>
+      <color rgb="FF9C0006"/>
+      <name val="MS PGothic"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF9C0006"/>
+      <name val="Tahoma"/>
+      <family val="2"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF000000"/>
+      <name val="Tahoma"/>
+      <family val="2"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="Tahoma"/>
+      <family val="2"/>
+    </font>
+    <font>
       <u/>
       <sz val="11"/>
       <color rgb="FF000000"/>
       <name val="Tahoma"/>
+      <family val="2"/>
     </font>
   </fonts>
-  <fills count="7">
+  <fills count="8">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -485,8 +556,13 @@
         <bgColor rgb="FFEFEFEF"/>
       </patternFill>
     </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFC7CE"/>
+      </patternFill>
+    </fill>
   </fills>
-  <borders count="11">
+  <borders count="12">
     <border>
       <left/>
       <right/>
@@ -612,11 +688,27 @@
       </bottom>
       <diagonal/>
     </border>
+    <border>
+      <left style="thin">
+        <color indexed="64"/>
+      </left>
+      <right style="thin">
+        <color indexed="64"/>
+      </right>
+      <top style="thin">
+        <color indexed="64"/>
+      </top>
+      <bottom style="thin">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
   </borders>
-  <cellStyleXfs count="1">
+  <cellStyleXfs count="2">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="10" fillId="7" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="43">
+  <cellXfs count="49">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
     <xf numFmtId="0" fontId="2" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1"/>
     <xf numFmtId="0" fontId="3" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1"/>
@@ -653,7 +745,7 @@
     <xf numFmtId="0" fontId="7" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="165" fontId="8" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="164" fontId="8" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="top"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1"/>
@@ -669,39 +761,52 @@
     <xf numFmtId="0" fontId="9" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="11" fillId="7" borderId="11" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="3" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="top"/>
     </xf>
     <xf numFmtId="0" fontId="5" fillId="3" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="5" fillId="3" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="5" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="5" fillId="3" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="6" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1"/>
     <xf numFmtId="0" fontId="5" fillId="3" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="3" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="top"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1"/>
-    <xf numFmtId="0" fontId="2" fillId="5" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1"/>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="6" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1"/>
-    <xf numFmtId="0" fontId="2" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1"/>
   </cellXfs>
-  <cellStyles count="1">
+  <cellStyles count="2">
+    <cellStyle name="Bad" xfId="1" builtinId="27"/>
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
   <dxfs count="0"/>
@@ -941,9 +1046,9 @@
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="30"/>
-      <c r="C1" s="31"/>
-      <c r="D1" s="31"/>
+      <c r="B1" s="29"/>
+      <c r="C1" s="30"/>
+      <c r="D1" s="30"/>
       <c r="E1" s="2"/>
       <c r="F1" s="2"/>
       <c r="G1" s="2"/>
@@ -970,9 +1075,9 @@
     </row>
     <row r="2" spans="1:27" ht="13.8" x14ac:dyDescent="0.25">
       <c r="A2" s="2"/>
-      <c r="B2" s="29"/>
-      <c r="C2" s="29"/>
-      <c r="D2" s="29"/>
+      <c r="B2" s="31"/>
+      <c r="C2" s="31"/>
+      <c r="D2" s="31"/>
       <c r="E2" s="2"/>
       <c r="F2" s="2"/>
       <c r="G2" s="2"/>
@@ -1004,8 +1109,8 @@
       <c r="B3" s="32" t="s">
         <v>2</v>
       </c>
-      <c r="C3" s="25"/>
-      <c r="D3" s="27"/>
+      <c r="C3" s="33"/>
+      <c r="D3" s="34"/>
       <c r="E3" s="2"/>
       <c r="F3" s="2"/>
       <c r="G3" s="2"/>
@@ -1034,11 +1139,11 @@
       <c r="A4" s="4" t="s">
         <v>3</v>
       </c>
-      <c r="B4" s="33" t="s">
+      <c r="B4" s="35" t="s">
         <v>20</v>
       </c>
-      <c r="C4" s="25"/>
-      <c r="D4" s="27"/>
+      <c r="C4" s="33"/>
+      <c r="D4" s="34"/>
       <c r="E4" s="2"/>
       <c r="F4" s="2"/>
       <c r="G4" s="2"/>
@@ -1070,8 +1175,8 @@
       <c r="B5" s="32" t="s">
         <v>21</v>
       </c>
-      <c r="C5" s="25"/>
-      <c r="D5" s="27"/>
+      <c r="C5" s="33"/>
+      <c r="D5" s="34"/>
       <c r="E5" s="2"/>
       <c r="F5" s="2"/>
       <c r="G5" s="2"/>
@@ -1101,7 +1206,7 @@
         <v>5</v>
       </c>
       <c r="B6" s="6">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="C6" s="7" t="s">
         <v>6</v>
@@ -1138,7 +1243,7 @@
         <v>7</v>
       </c>
       <c r="B7" s="6">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="C7" s="9" t="s">
         <v>8</v>
@@ -1200,39 +1305,39 @@
       <c r="AA8" s="3"/>
     </row>
     <row r="9" spans="1:27" ht="13.8" x14ac:dyDescent="0.25">
-      <c r="A9" s="34" t="s">
+      <c r="A9" s="36" t="s">
         <v>9</v>
       </c>
-      <c r="B9" s="35" t="s">
+      <c r="B9" s="38" t="s">
         <v>10</v>
       </c>
-      <c r="C9" s="34" t="s">
+      <c r="C9" s="36" t="s">
         <v>11</v>
       </c>
-      <c r="D9" s="36" t="s">
+      <c r="D9" s="44" t="s">
         <v>12</v>
       </c>
-      <c r="E9" s="31"/>
-      <c r="F9" s="31"/>
-      <c r="G9" s="34" t="s">
+      <c r="E9" s="30"/>
+      <c r="F9" s="30"/>
+      <c r="G9" s="36" t="s">
         <v>13</v>
       </c>
-      <c r="H9" s="37" t="s">
+      <c r="H9" s="41" t="s">
         <v>14</v>
       </c>
-      <c r="I9" s="37" t="s">
+      <c r="I9" s="41" t="s">
         <v>15</v>
       </c>
-      <c r="J9" s="37" t="s">
+      <c r="J9" s="41" t="s">
         <v>16</v>
       </c>
-      <c r="K9" s="37" t="s">
+      <c r="K9" s="41" t="s">
         <v>17</v>
       </c>
-      <c r="L9" s="37" t="s">
+      <c r="L9" s="41" t="s">
         <v>18</v>
       </c>
-      <c r="M9" s="37" t="s">
+      <c r="M9" s="41" t="s">
         <v>19</v>
       </c>
       <c r="N9" s="3"/>
@@ -1251,19 +1356,19 @@
       <c r="AA9" s="3"/>
     </row>
     <row r="10" spans="1:27" ht="13.8" x14ac:dyDescent="0.25">
-      <c r="A10" s="26"/>
-      <c r="B10" s="26"/>
-      <c r="C10" s="26"/>
-      <c r="D10" s="28"/>
-      <c r="E10" s="29"/>
-      <c r="F10" s="29"/>
-      <c r="G10" s="26"/>
-      <c r="H10" s="26"/>
-      <c r="I10" s="26"/>
-      <c r="J10" s="26"/>
-      <c r="K10" s="26"/>
-      <c r="L10" s="26"/>
-      <c r="M10" s="26"/>
+      <c r="A10" s="37"/>
+      <c r="B10" s="37"/>
+      <c r="C10" s="37"/>
+      <c r="D10" s="45"/>
+      <c r="E10" s="31"/>
+      <c r="F10" s="31"/>
+      <c r="G10" s="37"/>
+      <c r="H10" s="37"/>
+      <c r="I10" s="37"/>
+      <c r="J10" s="37"/>
+      <c r="K10" s="37"/>
+      <c r="L10" s="37"/>
+      <c r="M10" s="37"/>
       <c r="N10" s="3"/>
       <c r="O10" s="3"/>
       <c r="P10" s="3"/>
@@ -1281,18 +1386,18 @@
     </row>
     <row r="11" spans="1:27" ht="13.8" x14ac:dyDescent="0.25">
       <c r="A11" s="13"/>
-      <c r="B11" s="38"/>
-      <c r="C11" s="25"/>
-      <c r="D11" s="25"/>
-      <c r="E11" s="25"/>
-      <c r="F11" s="25"/>
-      <c r="G11" s="25"/>
-      <c r="H11" s="25"/>
-      <c r="I11" s="25"/>
-      <c r="J11" s="25"/>
-      <c r="K11" s="25"/>
-      <c r="L11" s="25"/>
-      <c r="M11" s="25"/>
+      <c r="B11" s="46"/>
+      <c r="C11" s="33"/>
+      <c r="D11" s="33"/>
+      <c r="E11" s="33"/>
+      <c r="F11" s="33"/>
+      <c r="G11" s="33"/>
+      <c r="H11" s="33"/>
+      <c r="I11" s="33"/>
+      <c r="J11" s="33"/>
+      <c r="K11" s="33"/>
+      <c r="L11" s="33"/>
+      <c r="M11" s="33"/>
       <c r="N11" s="3"/>
       <c r="O11" s="3"/>
       <c r="P11" s="3"/>
@@ -1309,21 +1414,21 @@
       <c r="AA11" s="3"/>
     </row>
     <row r="12" spans="1:27" ht="13.8" x14ac:dyDescent="0.25">
-      <c r="A12" s="39" t="s">
+      <c r="A12" s="40" t="s">
         <v>22</v>
       </c>
-      <c r="B12" s="25"/>
-      <c r="C12" s="25"/>
-      <c r="D12" s="25"/>
-      <c r="E12" s="25"/>
-      <c r="F12" s="25"/>
-      <c r="G12" s="25"/>
-      <c r="H12" s="25"/>
-      <c r="I12" s="25"/>
-      <c r="J12" s="25"/>
-      <c r="K12" s="25"/>
-      <c r="L12" s="25"/>
-      <c r="M12" s="27"/>
+      <c r="B12" s="33"/>
+      <c r="C12" s="33"/>
+      <c r="D12" s="33"/>
+      <c r="E12" s="33"/>
+      <c r="F12" s="33"/>
+      <c r="G12" s="33"/>
+      <c r="H12" s="33"/>
+      <c r="I12" s="33"/>
+      <c r="J12" s="33"/>
+      <c r="K12" s="33"/>
+      <c r="L12" s="33"/>
+      <c r="M12" s="34"/>
       <c r="N12" s="3"/>
       <c r="O12" s="3"/>
       <c r="P12" s="3"/>
@@ -1349,11 +1454,11 @@
       <c r="C13" s="16" t="s">
         <v>25</v>
       </c>
-      <c r="D13" s="40" t="s">
+      <c r="D13" s="39" t="s">
         <v>26</v>
       </c>
-      <c r="E13" s="25"/>
-      <c r="F13" s="25"/>
+      <c r="E13" s="33"/>
+      <c r="F13" s="33"/>
       <c r="G13" s="17" t="s">
         <v>27</v>
       </c>
@@ -1394,11 +1499,11 @@
       <c r="C14" s="16" t="s">
         <v>31</v>
       </c>
-      <c r="D14" s="40" t="s">
+      <c r="D14" s="39" t="s">
         <v>32</v>
       </c>
-      <c r="E14" s="25"/>
-      <c r="F14" s="25"/>
+      <c r="E14" s="33"/>
+      <c r="F14" s="33"/>
       <c r="G14" s="17" t="s">
         <v>33</v>
       </c>
@@ -1436,21 +1541,21 @@
       <c r="AA14" s="3"/>
     </row>
     <row r="15" spans="1:27" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A15" s="39" t="s">
+      <c r="A15" s="40" t="s">
         <v>36</v>
       </c>
-      <c r="B15" s="25"/>
-      <c r="C15" s="25"/>
-      <c r="D15" s="25"/>
-      <c r="E15" s="25"/>
-      <c r="F15" s="25"/>
-      <c r="G15" s="25"/>
-      <c r="H15" s="25"/>
-      <c r="I15" s="25"/>
-      <c r="J15" s="25"/>
-      <c r="K15" s="25"/>
-      <c r="L15" s="25"/>
-      <c r="M15" s="27"/>
+      <c r="B15" s="33"/>
+      <c r="C15" s="33"/>
+      <c r="D15" s="33"/>
+      <c r="E15" s="33"/>
+      <c r="F15" s="33"/>
+      <c r="G15" s="33"/>
+      <c r="H15" s="33"/>
+      <c r="I15" s="33"/>
+      <c r="J15" s="33"/>
+      <c r="K15" s="33"/>
+      <c r="L15" s="33"/>
+      <c r="M15" s="34"/>
       <c r="N15" s="3"/>
       <c r="O15" s="3"/>
       <c r="P15" s="3"/>
@@ -1476,11 +1581,11 @@
       <c r="C16" s="16" t="s">
         <v>39</v>
       </c>
-      <c r="D16" s="40" t="s">
+      <c r="D16" s="39" t="s">
         <v>40</v>
       </c>
-      <c r="E16" s="25"/>
-      <c r="F16" s="25"/>
+      <c r="E16" s="33"/>
+      <c r="F16" s="33"/>
       <c r="G16" s="17" t="s">
         <v>41</v>
       </c>
@@ -1518,21 +1623,21 @@
       <c r="AA16" s="3"/>
     </row>
     <row r="17" spans="1:27" ht="13.8" x14ac:dyDescent="0.25">
-      <c r="A17" s="39" t="s">
+      <c r="A17" s="40" t="s">
         <v>44</v>
       </c>
-      <c r="B17" s="25"/>
-      <c r="C17" s="25"/>
-      <c r="D17" s="25"/>
-      <c r="E17" s="25"/>
-      <c r="F17" s="25"/>
-      <c r="G17" s="25"/>
-      <c r="H17" s="25"/>
-      <c r="I17" s="25"/>
-      <c r="J17" s="25"/>
-      <c r="K17" s="25"/>
-      <c r="L17" s="25"/>
-      <c r="M17" s="27"/>
+      <c r="B17" s="33"/>
+      <c r="C17" s="33"/>
+      <c r="D17" s="33"/>
+      <c r="E17" s="33"/>
+      <c r="F17" s="33"/>
+      <c r="G17" s="33"/>
+      <c r="H17" s="33"/>
+      <c r="I17" s="33"/>
+      <c r="J17" s="33"/>
+      <c r="K17" s="33"/>
+      <c r="L17" s="33"/>
+      <c r="M17" s="34"/>
       <c r="N17" s="3"/>
       <c r="O17" s="3"/>
       <c r="P17" s="3"/>
@@ -1548,23 +1653,23 @@
       <c r="Z17" s="3"/>
       <c r="AA17" s="3"/>
     </row>
-    <row r="18" spans="1:27" ht="141.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="18" spans="1:27" ht="162" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A18" s="14" t="s">
         <v>45</v>
       </c>
-      <c r="B18" s="15" t="s">
+      <c r="B18" s="28" t="s">
         <v>46</v>
       </c>
-      <c r="C18" s="16" t="s">
+      <c r="C18" s="27" t="s">
+        <v>96</v>
+      </c>
+      <c r="D18" s="39" t="s">
         <v>47</v>
       </c>
-      <c r="D18" s="40" t="s">
+      <c r="E18" s="33"/>
+      <c r="F18" s="33"/>
+      <c r="G18" s="17" t="s">
         <v>48</v>
-      </c>
-      <c r="E18" s="25"/>
-      <c r="F18" s="25"/>
-      <c r="G18" s="17" t="s">
-        <v>49</v>
       </c>
       <c r="H18" s="18">
         <v>46248</v>
@@ -1573,7 +1678,7 @@
         <v>5</v>
       </c>
       <c r="J18" s="16" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="K18" s="18"/>
       <c r="L18" s="14"/>
@@ -1595,21 +1700,21 @@
     </row>
     <row r="19" spans="1:27" ht="192.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A19" s="14" t="s">
+        <v>50</v>
+      </c>
+      <c r="B19" s="15" t="s">
         <v>51</v>
       </c>
-      <c r="B19" s="15" t="s">
+      <c r="C19" s="27" t="s">
+        <v>97</v>
+      </c>
+      <c r="D19" s="39" t="s">
         <v>52</v>
       </c>
-      <c r="C19" s="16" t="s">
+      <c r="E19" s="33"/>
+      <c r="F19" s="33"/>
+      <c r="G19" s="17" t="s">
         <v>53</v>
-      </c>
-      <c r="D19" s="40" t="s">
-        <v>54</v>
-      </c>
-      <c r="E19" s="25"/>
-      <c r="F19" s="25"/>
-      <c r="G19" s="17" t="s">
-        <v>55</v>
       </c>
       <c r="H19" s="18">
         <v>46248</v>
@@ -1618,7 +1723,7 @@
         <v>5</v>
       </c>
       <c r="J19" s="16" t="s">
-        <v>56</v>
+        <v>54</v>
       </c>
       <c r="K19" s="18"/>
       <c r="L19" s="14"/>
@@ -1639,21 +1744,21 @@
       <c r="AA19" s="3"/>
     </row>
     <row r="20" spans="1:27" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A20" s="39" t="s">
-        <v>57</v>
+      <c r="A20" s="40" t="s">
+        <v>55</v>
       </c>
-      <c r="B20" s="25"/>
-      <c r="C20" s="25"/>
-      <c r="D20" s="25"/>
-      <c r="E20" s="25"/>
-      <c r="F20" s="25"/>
-      <c r="G20" s="25"/>
-      <c r="H20" s="25"/>
-      <c r="I20" s="25"/>
-      <c r="J20" s="25"/>
-      <c r="K20" s="25"/>
-      <c r="L20" s="25"/>
-      <c r="M20" s="27"/>
+      <c r="B20" s="33"/>
+      <c r="C20" s="33"/>
+      <c r="D20" s="33"/>
+      <c r="E20" s="33"/>
+      <c r="F20" s="33"/>
+      <c r="G20" s="33"/>
+      <c r="H20" s="33"/>
+      <c r="I20" s="33"/>
+      <c r="J20" s="33"/>
+      <c r="K20" s="33"/>
+      <c r="L20" s="33"/>
+      <c r="M20" s="34"/>
       <c r="N20" s="3"/>
       <c r="O20" s="3"/>
       <c r="P20" s="3"/>
@@ -1671,21 +1776,21 @@
     </row>
     <row r="21" spans="1:27" ht="162.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A21" s="14" t="s">
+        <v>56</v>
+      </c>
+      <c r="B21" s="15" t="s">
+        <v>57</v>
+      </c>
+      <c r="C21" s="16" t="s">
         <v>58</v>
       </c>
-      <c r="B21" s="15" t="s">
+      <c r="D21" s="39" t="s">
         <v>59</v>
       </c>
-      <c r="C21" s="16" t="s">
+      <c r="E21" s="33"/>
+      <c r="F21" s="33"/>
+      <c r="G21" s="17" t="s">
         <v>60</v>
-      </c>
-      <c r="D21" s="40" t="s">
-        <v>61</v>
-      </c>
-      <c r="E21" s="25"/>
-      <c r="F21" s="25"/>
-      <c r="G21" s="17" t="s">
-        <v>62</v>
       </c>
       <c r="H21" s="18">
         <v>46248</v>
@@ -1694,7 +1799,7 @@
         <v>7</v>
       </c>
       <c r="J21" s="16" t="s">
-        <v>63</v>
+        <v>61</v>
       </c>
       <c r="K21" s="18">
         <v>46249</v>
@@ -1703,7 +1808,7 @@
         <v>5</v>
       </c>
       <c r="M21" s="17" t="s">
-        <v>64</v>
+        <v>62</v>
       </c>
       <c r="N21" s="3"/>
       <c r="O21" s="3"/>
@@ -1721,53 +1826,53 @@
       <c r="AA21" s="3"/>
     </row>
     <row r="22" spans="1:27" ht="13.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A22" s="39" t="s">
+      <c r="A22" s="40" t="s">
+        <v>63</v>
+      </c>
+      <c r="B22" s="33"/>
+      <c r="C22" s="33"/>
+      <c r="D22" s="33"/>
+      <c r="E22" s="33"/>
+      <c r="F22" s="33"/>
+      <c r="G22" s="33"/>
+      <c r="H22" s="33"/>
+      <c r="I22" s="33"/>
+      <c r="J22" s="33"/>
+      <c r="K22" s="33"/>
+      <c r="L22" s="33"/>
+      <c r="M22" s="34"/>
+      <c r="N22" s="42"/>
+      <c r="O22" s="30"/>
+      <c r="P22" s="30"/>
+      <c r="Q22" s="30"/>
+      <c r="R22" s="30"/>
+      <c r="S22" s="30"/>
+      <c r="T22" s="30"/>
+      <c r="U22" s="30"/>
+      <c r="V22" s="30"/>
+      <c r="W22" s="30"/>
+      <c r="X22" s="30"/>
+      <c r="Y22" s="30"/>
+      <c r="Z22" s="30"/>
+      <c r="AA22" s="3"/>
+    </row>
+    <row r="23" spans="1:27" ht="155.25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A23" s="14" t="s">
+        <v>64</v>
+      </c>
+      <c r="B23" s="15" t="s">
         <v>65</v>
       </c>
-      <c r="B22" s="25"/>
-      <c r="C22" s="25"/>
-      <c r="D22" s="25"/>
-      <c r="E22" s="25"/>
-      <c r="F22" s="25"/>
-      <c r="G22" s="25"/>
-      <c r="H22" s="25"/>
-      <c r="I22" s="25"/>
-      <c r="J22" s="25"/>
-      <c r="K22" s="25"/>
-      <c r="L22" s="25"/>
-      <c r="M22" s="27"/>
-      <c r="N22" s="41"/>
-      <c r="O22" s="31"/>
-      <c r="P22" s="31"/>
-      <c r="Q22" s="31"/>
-      <c r="R22" s="31"/>
-      <c r="S22" s="31"/>
-      <c r="T22" s="31"/>
-      <c r="U22" s="31"/>
-      <c r="V22" s="31"/>
-      <c r="W22" s="31"/>
-      <c r="X22" s="31"/>
-      <c r="Y22" s="31"/>
-      <c r="Z22" s="31"/>
-      <c r="AA22" s="3"/>
-    </row>
-    <row r="23" spans="1:27" ht="155.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A23" s="14" t="s">
+      <c r="C23" s="16" t="s">
         <v>66</v>
       </c>
-      <c r="B23" s="15" t="s">
+      <c r="D23" s="39" t="s">
         <v>67</v>
       </c>
-      <c r="C23" s="16" t="s">
+      <c r="E23" s="33"/>
+      <c r="F23" s="33"/>
+      <c r="G23" s="23" t="s">
         <v>68</v>
-      </c>
-      <c r="D23" s="40" t="s">
-        <v>69</v>
-      </c>
-      <c r="E23" s="25"/>
-      <c r="F23" s="25"/>
-      <c r="G23" s="23" t="s">
-        <v>70</v>
       </c>
       <c r="H23" s="18">
         <v>46248</v>
@@ -1776,7 +1881,7 @@
         <v>7</v>
       </c>
       <c r="J23" s="16" t="s">
-        <v>71</v>
+        <v>69</v>
       </c>
       <c r="K23" s="18">
         <v>46249</v>
@@ -1785,7 +1890,7 @@
         <v>5</v>
       </c>
       <c r="M23" s="17" t="s">
-        <v>72</v>
+        <v>70</v>
       </c>
       <c r="N23" s="3"/>
       <c r="O23" s="3"/>
@@ -1803,62 +1908,62 @@
       <c r="AA23" s="3"/>
     </row>
     <row r="24" spans="1:27" ht="13.8" x14ac:dyDescent="0.25">
-      <c r="A24" s="39" t="s">
-        <v>73</v>
+      <c r="A24" s="40" t="s">
+        <v>71</v>
       </c>
-      <c r="B24" s="25"/>
-      <c r="C24" s="25"/>
-      <c r="D24" s="25"/>
-      <c r="E24" s="25"/>
-      <c r="F24" s="25"/>
-      <c r="G24" s="25"/>
-      <c r="H24" s="25"/>
-      <c r="I24" s="25"/>
-      <c r="J24" s="25"/>
-      <c r="K24" s="25"/>
-      <c r="L24" s="25"/>
-      <c r="M24" s="27"/>
-      <c r="N24" s="42"/>
-      <c r="O24" s="31"/>
-      <c r="P24" s="31"/>
-      <c r="Q24" s="31"/>
-      <c r="R24" s="31"/>
-      <c r="S24" s="31"/>
-      <c r="T24" s="31"/>
-      <c r="U24" s="31"/>
-      <c r="V24" s="31"/>
-      <c r="W24" s="31"/>
-      <c r="X24" s="31"/>
-      <c r="Y24" s="31"/>
-      <c r="Z24" s="31"/>
+      <c r="B24" s="33"/>
+      <c r="C24" s="33"/>
+      <c r="D24" s="33"/>
+      <c r="E24" s="33"/>
+      <c r="F24" s="33"/>
+      <c r="G24" s="33"/>
+      <c r="H24" s="33"/>
+      <c r="I24" s="33"/>
+      <c r="J24" s="33"/>
+      <c r="K24" s="33"/>
+      <c r="L24" s="33"/>
+      <c r="M24" s="34"/>
+      <c r="N24" s="43"/>
+      <c r="O24" s="30"/>
+      <c r="P24" s="30"/>
+      <c r="Q24" s="30"/>
+      <c r="R24" s="30"/>
+      <c r="S24" s="30"/>
+      <c r="T24" s="30"/>
+      <c r="U24" s="30"/>
+      <c r="V24" s="30"/>
+      <c r="W24" s="30"/>
+      <c r="X24" s="30"/>
+      <c r="Y24" s="30"/>
+      <c r="Z24" s="30"/>
       <c r="AA24" s="3"/>
     </row>
     <row r="25" spans="1:27" ht="165" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A25" s="14" t="s">
-        <v>74</v>
+        <v>72</v>
       </c>
       <c r="B25" s="15" t="s">
-        <v>75</v>
+        <v>98</v>
       </c>
       <c r="C25" s="16" t="s">
-        <v>76</v>
+        <v>99</v>
       </c>
-      <c r="D25" s="40" t="s">
-        <v>77</v>
+      <c r="D25" s="39" t="s">
+        <v>100</v>
       </c>
-      <c r="E25" s="25"/>
-      <c r="F25" s="25"/>
-      <c r="G25" s="17" t="s">
-        <v>78</v>
+      <c r="E25" s="33"/>
+      <c r="F25" s="33"/>
+      <c r="G25" s="23" t="s">
+        <v>101</v>
       </c>
       <c r="H25" s="18">
         <v>46248</v>
       </c>
-      <c r="I25" s="14" t="s">
-        <v>7</v>
+      <c r="I25" s="47" t="s">
+        <v>5</v>
       </c>
-      <c r="J25" s="16" t="s">
-        <v>79</v>
+      <c r="J25" s="27" t="s">
+        <v>102</v>
       </c>
       <c r="K25" s="18"/>
       <c r="L25" s="14"/>
@@ -1879,22 +1984,22 @@
       <c r="AA25" s="3"/>
     </row>
     <row r="26" spans="1:27" ht="174" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A26" s="14" t="s">
-        <v>80</v>
+      <c r="A26" s="47" t="s">
+        <v>73</v>
       </c>
       <c r="B26" s="15" t="s">
-        <v>81</v>
+        <v>74</v>
       </c>
       <c r="C26" s="16" t="s">
-        <v>82</v>
+        <v>75</v>
       </c>
-      <c r="D26" s="40" t="s">
-        <v>83</v>
+      <c r="D26" s="39" t="s">
+        <v>76</v>
       </c>
-      <c r="E26" s="25"/>
-      <c r="F26" s="25"/>
-      <c r="G26" s="24" t="s">
-        <v>84</v>
+      <c r="E26" s="33"/>
+      <c r="F26" s="33"/>
+      <c r="G26" s="48" t="s">
+        <v>77</v>
       </c>
       <c r="H26" s="18">
         <v>46248</v>
@@ -1903,7 +2008,7 @@
         <v>7</v>
       </c>
       <c r="J26" s="16" t="s">
-        <v>85</v>
+        <v>78</v>
       </c>
       <c r="K26" s="18"/>
       <c r="L26" s="14"/>
@@ -29898,9 +30003,208 @@
     <hyperlink ref="M21" r:id="rId9" xr:uid="{00000000-0004-0000-0B00-000008000000}"/>
     <hyperlink ref="G23" r:id="rId10" xr:uid="{00000000-0004-0000-0B00-000009000000}"/>
     <hyperlink ref="M23" r:id="rId11" xr:uid="{00000000-0004-0000-0B00-00000A000000}"/>
-    <hyperlink ref="G25" r:id="rId12" xr:uid="{00000000-0004-0000-0B00-00000B000000}"/>
-    <hyperlink ref="G26" r:id="rId13" xr:uid="{00000000-0004-0000-0B00-00000C000000}"/>
+    <hyperlink ref="G26" r:id="rId12" xr:uid="{00000000-0004-0000-0B00-00000C000000}"/>
   </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup orientation="portrait" r:id="rId13"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{7FBAECCD-A664-4798-A72B-8871055C7066}">
+  <dimension ref="A1:J10"/>
+  <sheetFormatPr defaultRowHeight="13.8" x14ac:dyDescent="0.25"/>
+  <cols>
+    <col min="1" max="1" width="24.21875" style="25" customWidth="1"/>
+    <col min="2" max="3" width="18.88671875" style="25" customWidth="1"/>
+    <col min="4" max="4" width="24.21875" style="25" customWidth="1"/>
+    <col min="5" max="5" width="19.33203125" style="25" customWidth="1"/>
+    <col min="6" max="6" width="17" style="25" customWidth="1"/>
+    <col min="7" max="7" width="17.21875" style="25" customWidth="1"/>
+    <col min="8" max="8" width="17.109375" style="25" customWidth="1"/>
+    <col min="9" max="9" width="26.6640625" style="25" customWidth="1"/>
+    <col min="10" max="10" width="33.77734375" style="25" customWidth="1"/>
+    <col min="11" max="16384" width="8.88671875" style="25"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A1" s="24" t="s">
+        <v>79</v>
+      </c>
+      <c r="B1" s="24" t="s">
+        <v>83</v>
+      </c>
+      <c r="C1" s="24" t="s">
+        <v>80</v>
+      </c>
+      <c r="D1" s="24" t="s">
+        <v>81</v>
+      </c>
+      <c r="E1" s="24" t="s">
+        <v>82</v>
+      </c>
+      <c r="F1" s="24" t="s">
+        <v>88</v>
+      </c>
+      <c r="G1" s="24" t="s">
+        <v>89</v>
+      </c>
+      <c r="H1" s="24" t="s">
+        <v>90</v>
+      </c>
+      <c r="I1" s="24" t="s">
+        <v>91</v>
+      </c>
+      <c r="J1" s="24" t="s">
+        <v>92</v>
+      </c>
+    </row>
+    <row r="2" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A2" s="26" t="s">
+        <v>23</v>
+      </c>
+      <c r="B2" s="26" t="s">
+        <v>84</v>
+      </c>
+      <c r="C2" s="26" t="s">
+        <v>85</v>
+      </c>
+      <c r="D2" s="26" t="s">
+        <v>86</v>
+      </c>
+      <c r="E2" s="26" t="s">
+        <v>87</v>
+      </c>
+      <c r="F2" s="26" t="s">
+        <v>95</v>
+      </c>
+      <c r="G2" s="26" t="s">
+        <v>85</v>
+      </c>
+      <c r="H2" s="26">
+        <v>1</v>
+      </c>
+      <c r="I2" s="26" t="s">
+        <v>94</v>
+      </c>
+      <c r="J2" s="26" t="s">
+        <v>93</v>
+      </c>
+    </row>
+    <row r="3" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A3" s="26" t="s">
+        <v>29</v>
+      </c>
+      <c r="B3" s="26"/>
+      <c r="C3" s="26"/>
+      <c r="D3" s="26"/>
+      <c r="E3" s="26"/>
+      <c r="F3" s="26"/>
+      <c r="G3" s="26"/>
+      <c r="H3" s="26"/>
+      <c r="I3" s="26"/>
+      <c r="J3" s="26"/>
+    </row>
+    <row r="4" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A4" s="26" t="s">
+        <v>37</v>
+      </c>
+      <c r="B4" s="26"/>
+      <c r="C4" s="26"/>
+      <c r="D4" s="26"/>
+      <c r="E4" s="26"/>
+      <c r="F4" s="26"/>
+      <c r="G4" s="26"/>
+      <c r="H4" s="26"/>
+      <c r="I4" s="26"/>
+      <c r="J4" s="26"/>
+    </row>
+    <row r="5" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A5" s="26" t="s">
+        <v>45</v>
+      </c>
+      <c r="B5" s="26"/>
+      <c r="C5" s="26"/>
+      <c r="D5" s="26"/>
+      <c r="E5" s="26"/>
+      <c r="F5" s="26"/>
+      <c r="G5" s="26"/>
+      <c r="H5" s="26"/>
+      <c r="I5" s="26"/>
+      <c r="J5" s="26"/>
+    </row>
+    <row r="6" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A6" s="26" t="s">
+        <v>50</v>
+      </c>
+      <c r="B6" s="26"/>
+      <c r="C6" s="26"/>
+      <c r="D6" s="26"/>
+      <c r="E6" s="26"/>
+      <c r="F6" s="26"/>
+      <c r="G6" s="26"/>
+      <c r="H6" s="26"/>
+      <c r="I6" s="26"/>
+      <c r="J6" s="26"/>
+    </row>
+    <row r="7" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A7" s="26" t="s">
+        <v>56</v>
+      </c>
+      <c r="B7" s="26"/>
+      <c r="C7" s="26"/>
+      <c r="D7" s="26"/>
+      <c r="E7" s="26"/>
+      <c r="F7" s="26"/>
+      <c r="G7" s="26"/>
+      <c r="H7" s="26"/>
+      <c r="I7" s="26"/>
+      <c r="J7" s="26"/>
+    </row>
+    <row r="8" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A8" s="26" t="s">
+        <v>64</v>
+      </c>
+      <c r="B8" s="26"/>
+      <c r="C8" s="26"/>
+      <c r="D8" s="26"/>
+      <c r="E8" s="26"/>
+      <c r="F8" s="26"/>
+      <c r="G8" s="26"/>
+      <c r="H8" s="26"/>
+      <c r="I8" s="26"/>
+      <c r="J8" s="26"/>
+    </row>
+    <row r="9" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A9" s="26" t="s">
+        <v>72</v>
+      </c>
+      <c r="B9" s="26"/>
+      <c r="C9" s="26"/>
+      <c r="D9" s="26"/>
+      <c r="E9" s="26"/>
+      <c r="F9" s="26"/>
+      <c r="G9" s="26"/>
+      <c r="H9" s="26"/>
+      <c r="I9" s="26"/>
+      <c r="J9" s="26"/>
+    </row>
+    <row r="10" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A10" s="26" t="s">
+        <v>73</v>
+      </c>
+      <c r="B10" s="26"/>
+      <c r="C10" s="26"/>
+      <c r="D10" s="26"/>
+      <c r="E10" s="26"/>
+      <c r="F10" s="26"/>
+      <c r="G10" s="26"/>
+      <c r="H10" s="26"/>
+      <c r="I10" s="26"/>
+      <c r="J10" s="26"/>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup orientation="portrait" r:id="rId1"/>
 </worksheet>
 </file>
--- a/TestCases/Notification_TestCase.xlsx
+++ b/TestCases/Notification_TestCase.xlsx
@@ -8,13 +8,12 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\DoAnNganh\SpringMediCareWeb-Selenium-Testing\TestCases\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D1BD39C7-C933-4C0F-987A-FEA465679220}" xr6:coauthVersionLast="36" xr6:coauthVersionMax="36" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D3EE7AE2-013B-486A-AF11-C5A20ED6694D}" xr6:coauthVersionLast="36" xr6:coauthVersionMax="36" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="0" windowWidth="12012" windowHeight="6960" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="0" yWindow="0" windowWidth="12792" windowHeight="6960" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
-    <sheet name="NOTIFICATION" sheetId="12" r:id="rId1"/>
-    <sheet name="AUTOMATION_DATA" sheetId="13" r:id="rId2"/>
+    <sheet name="NOTIFICATION" sheetId="13" r:id="rId1"/>
   </sheets>
   <definedNames>
     <definedName name="ACTION">#REF!</definedName>
@@ -24,7 +23,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="126" uniqueCount="103">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="100" uniqueCount="87">
   <si>
     <t>TEST CASE</t>
   </si>
@@ -32,22 +31,22 @@
     <t>System Name：</t>
   </si>
   <si>
+    <t>Pass</t>
+  </si>
+  <si>
+    <t>Fail</t>
+  </si>
+  <si>
     <t>SpringMediCareWeb</t>
+  </si>
+  <si>
+    <t>Pending</t>
   </si>
   <si>
     <t>Module Code：</t>
   </si>
   <si>
     <t>Test requirement:</t>
-  </si>
-  <si>
-    <t>Pass</t>
-  </si>
-  <si>
-    <t>Pending</t>
-  </si>
-  <si>
-    <t>Fail</t>
   </si>
   <si>
     <t>Number of test cases:</t>
@@ -86,10 +85,10 @@
     <t>Retest Evidence</t>
   </si>
   <si>
-    <t>NOTIFICATION400 - Patient Notification Management</t>
+    <t>NOTIFICATION - Patient Notifications</t>
   </si>
   <si>
-    <t>NOTIFICATION1 - Manage Patient Notifications</t>
+    <t>Patient Notification</t>
   </si>
   <si>
     <t>1. Kiểm tra Patient nhận thông báo sau khi lịch hẹn được Admin thao tác</t>
@@ -98,7 +97,8 @@
     <t>TC-NOTIFICATION-001</t>
   </si>
   <si>
-    <t>Kiểm tra Patient nhận được thông báo đúng sau khi Admin xác nhận lịch hẹn mà Patient đã đặt.</t>
+    <t xml:space="preserve">Kiểm tra Patient nhận được thông báo đúng sau khi Admin xác nhận lịch hẹn mà Patient đã đặt.
+</t>
   </si>
   <si>
     <t xml:space="preserve">1: Patient thực hiện đặt một lịch khám hợp lệ.
@@ -195,6 +195,16 @@
     <t>Kiểm tra khi Patient phát sinh nhiều thông báo từ các sự kiện khác nhau, các thông báo được lưu thành các bản ghi riêng biệt và không ghi đè lẫn nhau.</t>
   </si>
   <si>
+    <t>1: Đăng nhập bằng Patient.
+2: Tạo một lịch hẹn mới hợp lệ.
+3: Đăng xuất Patient và đăng nhập bằng Admin.
+4: Mở trang Quản lý lịch hẹn và xác nhận lịch hẹn vừa tạo.
+5: Đăng xuất Admin và đăng nhập lại bằng Patient.
+6: Mở trang Thông báo.
+7: Kiểm tra thông báo mới của lịch vừa được xác nhận.
+8: Kiểm tra thông báo đã tồn tại trước đó vẫn còn hiển thị.</t>
+  </si>
+  <si>
     <t>Patient nhận được thông báo mới tương ứng với sự kiện vừa phát sinh.
 Thông báo mới được hiển thị trong danh sách Thông báo.
 Các thông báo đã tồn tại trước đó vẫn còn hiển thị, không bị mất hoặc ghi đè.
@@ -211,6 +221,13 @@
   </si>
   <si>
     <t>Kiểm tra thông báo được phân tách đúng giữa các tài khoản Patient, Patient này không xem được thông báo của Patient khác.</t>
+  </si>
+  <si>
+    <t>1: Đăng nhập bằng tài khoản patient_an.
+2: Mở trang Thông báo và ghi nhận danh sách thông báo đang hiển thị.
+3: Đăng xuất patient_an, sau đó đăng nhập bằng tài khoản patient_thu.
+4: Mở trang Thông báo và ghi nhận danh sách thông báo đang hiển thị.
+5: So sánh nội dung thông báo của hai Patient, xác nhận danh sách thông báo được hiển thị riêng theo từng tài khoản và không giống hoàn toàn nhau.</t>
   </si>
   <si>
     <t>Patient A chỉ xem được thông báo liên quan đến lịch hẹn của Patient A và không xem được thông báo của Patient B.
@@ -304,6 +321,29 @@
     <t>TC-NOTIFICATION-008</t>
   </si>
   <si>
+    <t>Kiểm tra Patient nhận được thông báo mới khi Doctor kê thêm một đơn thuốc mới cho Patient đã có đơn thuốc trước đó.</t>
+  </si>
+  <si>
+    <t>1: Chuẩn bị Patient đã có một đơn thuốc cũ.
+2: Ghi nhận notification của đơn thuốc cũ.
+3: Doctor đăng nhập.
+4: Mở hồ sơ bệnh án → tab Đơn thuốc.
+5: Kê thêm một đơn thuốc mới với thuốc/số lượng/liều dùng khác.
+6: Lưu đơn thuốc mới.
+7: Đăng xuất Doctor → đăng nhập Patient.
+8: Mở Thông báo.
+9: Tìm và kiểm tra thông báo mới phát sinh từ đơn thuốc vừa được lưu.</t>
+  </si>
+  <si>
+    <t>Đơn thuốc mới được lưu thành công. Patient nhận được một thông báo mới thuộc loại [Đơn thuốc]. Nội dung thông báo tương ứng với đơn thuốc mới vừa được tạo. Thông báo mới không bị nhầm hoặc ghi đè bởi thông báo của đơn thuốc trước đó. Thời gian thông báo được ghi nhận và hiển thị.</t>
+  </si>
+  <si>
+    <t>TCNotification8_1, TCNotification8_2, TCNotification8_3</t>
+  </si>
+  <si>
+    <t>Phát sinh đúng thông báo [Đơn thuốc] mới sau khi Doctor kê thêm đơn thuốc mới; thông báo cũ và mới được hiển thị riêng biệt.</t>
+  </si>
+  <si>
     <t>TC-NOTIFICATION-009</t>
   </si>
   <si>
@@ -330,98 +370,10 @@
     <t xml:space="preserve">TCNotification9_1, TCNotification9_2, TCNotification9_3, </t>
   </si>
   <si>
-    <t>Không phát sinh thông báo mới cho Patient sau khi Doctor cập nhật Chẩn đoán và Hướng điều trị của hồ sơ bệnh án.</t>
+    <t xml:space="preserve"> </t>
   </si>
   <si>
-    <t>test_case_id</t>
-  </si>
-  <si>
-    <t>patient_password</t>
-  </si>
-  <si>
-    <t>notification_type</t>
-  </si>
-  <si>
-    <t>expected_keyword</t>
-  </si>
-  <si>
-    <t>patient_username</t>
-  </si>
-  <si>
-    <t>patient_an</t>
-  </si>
-  <si>
-    <t>Abc@123</t>
-  </si>
-  <si>
-    <t>[Lịch hẹn]</t>
-  </si>
-  <si>
-    <t>da duoc xac nhan</t>
-  </si>
-  <si>
-    <t>admin_username</t>
-  </si>
-  <si>
-    <t>admin_password</t>
-  </si>
-  <si>
-    <t>doctor_id</t>
-  </si>
-  <si>
-    <t>time_format</t>
-  </si>
-  <si>
-    <t>note_prefix</t>
-  </si>
-  <si>
-    <t>SELENIUM-TC-NOTIFICATION-001-</t>
-  </si>
-  <si>
-    <t>%H:%M:%S %d/%m/%Y</t>
-  </si>
-  <si>
-    <t>admin_system</t>
-  </si>
-  <si>
-    <t>1: Đăng nhập bằng Patient.
-2: Tạo một lịch hẹn mới hợp lệ.
-3: Đăng xuất Patient và đăng nhập bằng Admin.
-4: Mở trang Quản lý lịch hẹn và xác nhận lịch hẹn vừa tạo.
-5: Đăng xuất Admin và đăng nhập lại bằng Patient.
-6: Mở trang Thông báo.
-7: Kiểm tra thông báo mới của lịch vừa được xác nhận.
-8: Kiểm tra thông báo đã tồn tại trước đó vẫn còn hiển thị.</t>
-  </si>
-  <si>
-    <t>1: Đăng nhập bằng tài khoản patient_an.
-2: Mở trang Thông báo và ghi nhận danh sách thông báo đang hiển thị.
-3: Đăng xuất patient_an, sau đó đăng nhập bằng tài khoản patient_thu.
-4: Mở trang Thông báo và ghi nhận danh sách thông báo đang hiển thị.
-5: So sánh nội dung thông báo của hai Patient, xác nhận danh sách thông báo được hiển thị riêng theo từng tài khoản và không giống hoàn toàn nhau.</t>
-  </si>
-  <si>
-    <t>Kiểm tra Patient nhận được thông báo mới khi Doctor kê thêm một đơn thuốc mới cho Patient đã có đơn thuốc trước đó.</t>
-  </si>
-  <si>
-    <t>1: Chuẩn bị Patient đã có một đơn thuốc cũ.
-2: Ghi nhận notification của đơn thuốc cũ.
-3: Doctor đăng nhập.
-4: Mở hồ sơ bệnh án → tab Đơn thuốc.
-5: Kê thêm một đơn thuốc mới với thuốc/số lượng/liều dùng khác.
-6: Lưu đơn thuốc mới.
-7: Đăng xuất Doctor → đăng nhập Patient.
-8: Mở Thông báo.
-9: Tìm và kiểm tra thông báo mới phát sinh từ đơn thuốc vừa được lưu.</t>
-  </si>
-  <si>
-    <t>Đơn thuốc mới được lưu thành công. Patient nhận được một thông báo mới thuộc loại [Đơn thuốc]. Nội dung thông báo tương ứng với đơn thuốc mới vừa được tạo. Thông báo mới không bị nhầm hoặc ghi đè bởi thông báo của đơn thuốc trước đó. Thời gian thông báo được ghi nhận và hiển thị.</t>
-  </si>
-  <si>
-    <t>TCNotification8_1, TCNotification8_2, TCNotification8_3</t>
-  </si>
-  <si>
-    <t>Phát sinh đúng thông báo [Đơn thuốc] mới sau khi Doctor kê thêm đơn thuốc mới; thông báo cũ và mới được hiển thị riêng biệt.</t>
+    <t>Không phát sinh thông báo mới cho Patient sau khi Doctor cập nhật Chẩn đoán và Hướng điều trị của hồ sơ bệnh án.</t>
   </si>
 </sst>
 </file>
@@ -429,9 +381,9 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
   <numFmts count="1">
-    <numFmt numFmtId="164" formatCode="d\-m"/>
+    <numFmt numFmtId="165" formatCode="d\-m"/>
   </numFmts>
-  <fonts count="15" x14ac:knownFonts="1">
+  <fonts count="11" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color rgb="FF000000"/>
@@ -487,39 +439,13 @@
       <name val="Tahoma"/>
     </font>
     <font>
-      <sz val="11"/>
-      <color rgb="FF9C0006"/>
-      <name val="MS PGothic"/>
-      <family val="2"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FF9C0006"/>
-      <name val="Tahoma"/>
-      <family val="2"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FF000000"/>
-      <name val="Tahoma"/>
-      <family val="2"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color theme="1"/>
-      <name val="Tahoma"/>
-      <family val="2"/>
-    </font>
-    <font>
       <u/>
       <sz val="11"/>
       <color rgb="FF000000"/>
       <name val="Tahoma"/>
-      <family val="2"/>
     </font>
   </fonts>
-  <fills count="8">
+  <fills count="7">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -556,13 +482,8 @@
         <bgColor rgb="FFEFEFEF"/>
       </patternFill>
     </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFC7CE"/>
-      </patternFill>
-    </fill>
   </fills>
-  <borders count="12">
+  <borders count="11">
     <border>
       <left/>
       <right/>
@@ -688,27 +609,11 @@
       </bottom>
       <diagonal/>
     </border>
-    <border>
-      <left style="thin">
-        <color indexed="64"/>
-      </left>
-      <right style="thin">
-        <color indexed="64"/>
-      </right>
-      <top style="thin">
-        <color indexed="64"/>
-      </top>
-      <bottom style="thin">
-        <color indexed="64"/>
-      </bottom>
-      <diagonal/>
-    </border>
   </borders>
-  <cellStyleXfs count="2">
+  <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
-    <xf numFmtId="0" fontId="10" fillId="7" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="49">
+  <cellXfs count="44">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
     <xf numFmtId="0" fontId="2" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1"/>
     <xf numFmtId="0" fontId="3" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1"/>
@@ -745,7 +650,7 @@
     <xf numFmtId="0" fontId="7" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="164" fontId="8" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="165" fontId="8" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="top"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1"/>
@@ -761,17 +666,14 @@
     <xf numFmtId="0" fontId="9" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="11" fillId="7" borderId="11" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1"/>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1"/>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="top" wrapText="1"/>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="top"/>
     </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
     <xf numFmtId="0" fontId="3" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1"/>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1"/>
@@ -784,29 +686,22 @@
     </xf>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="5" fillId="3" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1"/>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="5" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1"/>
-    <xf numFmtId="0" fontId="5" fillId="3" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="6" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1"/>
-    <xf numFmtId="0" fontId="2" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1"/>
     <xf numFmtId="0" fontId="5" fillId="3" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="5" fillId="3" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1"/>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="2" fillId="5" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="2" fillId="6" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1"/>
   </cellXfs>
-  <cellStyles count="2">
-    <cellStyle name="Bad" xfId="1" builtinId="27"/>
+  <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
   <dxfs count="0"/>
@@ -1023,7 +918,7 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0B00-000000000000}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0C00-000000000000}">
   <sheetPr>
     <outlinePr summaryBelow="0" summaryRight="0"/>
   </sheetPr>
@@ -1046,9 +941,9 @@
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="29"/>
-      <c r="C1" s="30"/>
-      <c r="D1" s="30"/>
+      <c r="B1" s="27"/>
+      <c r="C1" s="26"/>
+      <c r="D1" s="26"/>
       <c r="E1" s="2"/>
       <c r="F1" s="2"/>
       <c r="G1" s="2"/>
@@ -1075,9 +970,9 @@
     </row>
     <row r="2" spans="1:27" ht="13.8" x14ac:dyDescent="0.25">
       <c r="A2" s="2"/>
-      <c r="B2" s="31"/>
-      <c r="C2" s="31"/>
-      <c r="D2" s="31"/>
+      <c r="B2" s="28"/>
+      <c r="C2" s="28"/>
+      <c r="D2" s="28"/>
       <c r="E2" s="2"/>
       <c r="F2" s="2"/>
       <c r="G2" s="2"/>
@@ -1106,11 +1001,11 @@
       <c r="A3" s="4" t="s">
         <v>1</v>
       </c>
-      <c r="B3" s="32" t="s">
-        <v>2</v>
+      <c r="B3" s="29" t="s">
+        <v>4</v>
       </c>
-      <c r="C3" s="33"/>
-      <c r="D3" s="34"/>
+      <c r="C3" s="30"/>
+      <c r="D3" s="31"/>
       <c r="E3" s="2"/>
       <c r="F3" s="2"/>
       <c r="G3" s="2"/>
@@ -1137,13 +1032,13 @@
     </row>
     <row r="4" spans="1:27" ht="13.8" x14ac:dyDescent="0.25">
       <c r="A4" s="4" t="s">
-        <v>3</v>
+        <v>6</v>
       </c>
-      <c r="B4" s="35" t="s">
+      <c r="B4" s="32" t="s">
         <v>20</v>
       </c>
-      <c r="C4" s="33"/>
-      <c r="D4" s="34"/>
+      <c r="C4" s="30"/>
+      <c r="D4" s="31"/>
       <c r="E4" s="2"/>
       <c r="F4" s="2"/>
       <c r="G4" s="2"/>
@@ -1170,13 +1065,13 @@
     </row>
     <row r="5" spans="1:27" ht="13.8" x14ac:dyDescent="0.25">
       <c r="A5" s="4" t="s">
-        <v>4</v>
+        <v>7</v>
       </c>
-      <c r="B5" s="32" t="s">
+      <c r="B5" s="29" t="s">
         <v>21</v>
       </c>
-      <c r="C5" s="33"/>
-      <c r="D5" s="34"/>
+      <c r="C5" s="30"/>
+      <c r="D5" s="31"/>
       <c r="E5" s="2"/>
       <c r="F5" s="2"/>
       <c r="G5" s="2"/>
@@ -1203,13 +1098,13 @@
     </row>
     <row r="6" spans="1:27" ht="13.8" x14ac:dyDescent="0.25">
       <c r="A6" s="5" t="s">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="B6" s="6">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="C6" s="7" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="D6" s="8">
         <v>0</v>
@@ -1240,10 +1135,10 @@
     </row>
     <row r="7" spans="1:27" ht="13.8" x14ac:dyDescent="0.25">
       <c r="A7" s="5" t="s">
-        <v>7</v>
+        <v>3</v>
       </c>
       <c r="B7" s="6">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="C7" s="9" t="s">
         <v>8</v>
@@ -1305,39 +1200,39 @@
       <c r="AA8" s="3"/>
     </row>
     <row r="9" spans="1:27" ht="13.8" x14ac:dyDescent="0.25">
-      <c r="A9" s="36" t="s">
+      <c r="A9" s="33" t="s">
         <v>9</v>
       </c>
-      <c r="B9" s="38" t="s">
+      <c r="B9" s="35" t="s">
         <v>10</v>
       </c>
-      <c r="C9" s="36" t="s">
+      <c r="C9" s="33" t="s">
         <v>11</v>
       </c>
-      <c r="D9" s="44" t="s">
+      <c r="D9" s="36" t="s">
         <v>12</v>
       </c>
-      <c r="E9" s="30"/>
-      <c r="F9" s="30"/>
-      <c r="G9" s="36" t="s">
+      <c r="E9" s="26"/>
+      <c r="F9" s="26"/>
+      <c r="G9" s="33" t="s">
         <v>13</v>
       </c>
-      <c r="H9" s="41" t="s">
+      <c r="H9" s="38" t="s">
         <v>14</v>
       </c>
-      <c r="I9" s="41" t="s">
+      <c r="I9" s="38" t="s">
         <v>15</v>
       </c>
-      <c r="J9" s="41" t="s">
+      <c r="J9" s="38" t="s">
         <v>16</v>
       </c>
-      <c r="K9" s="41" t="s">
+      <c r="K9" s="38" t="s">
         <v>17</v>
       </c>
-      <c r="L9" s="41" t="s">
+      <c r="L9" s="38" t="s">
         <v>18</v>
       </c>
-      <c r="M9" s="41" t="s">
+      <c r="M9" s="38" t="s">
         <v>19</v>
       </c>
       <c r="N9" s="3"/>
@@ -1356,19 +1251,19 @@
       <c r="AA9" s="3"/>
     </row>
     <row r="10" spans="1:27" ht="13.8" x14ac:dyDescent="0.25">
-      <c r="A10" s="37"/>
-      <c r="B10" s="37"/>
-      <c r="C10" s="37"/>
-      <c r="D10" s="45"/>
-      <c r="E10" s="31"/>
-      <c r="F10" s="31"/>
-      <c r="G10" s="37"/>
-      <c r="H10" s="37"/>
-      <c r="I10" s="37"/>
-      <c r="J10" s="37"/>
-      <c r="K10" s="37"/>
-      <c r="L10" s="37"/>
-      <c r="M10" s="37"/>
+      <c r="A10" s="34"/>
+      <c r="B10" s="34"/>
+      <c r="C10" s="34"/>
+      <c r="D10" s="37"/>
+      <c r="E10" s="28"/>
+      <c r="F10" s="28"/>
+      <c r="G10" s="34"/>
+      <c r="H10" s="34"/>
+      <c r="I10" s="34"/>
+      <c r="J10" s="34"/>
+      <c r="K10" s="34"/>
+      <c r="L10" s="34"/>
+      <c r="M10" s="34"/>
       <c r="N10" s="3"/>
       <c r="O10" s="3"/>
       <c r="P10" s="3"/>
@@ -1386,18 +1281,18 @@
     </row>
     <row r="11" spans="1:27" ht="13.8" x14ac:dyDescent="0.25">
       <c r="A11" s="13"/>
-      <c r="B11" s="46"/>
-      <c r="C11" s="33"/>
-      <c r="D11" s="33"/>
-      <c r="E11" s="33"/>
-      <c r="F11" s="33"/>
-      <c r="G11" s="33"/>
-      <c r="H11" s="33"/>
-      <c r="I11" s="33"/>
-      <c r="J11" s="33"/>
-      <c r="K11" s="33"/>
-      <c r="L11" s="33"/>
-      <c r="M11" s="33"/>
+      <c r="B11" s="39"/>
+      <c r="C11" s="30"/>
+      <c r="D11" s="30"/>
+      <c r="E11" s="30"/>
+      <c r="F11" s="30"/>
+      <c r="G11" s="30"/>
+      <c r="H11" s="30"/>
+      <c r="I11" s="30"/>
+      <c r="J11" s="30"/>
+      <c r="K11" s="30"/>
+      <c r="L11" s="30"/>
+      <c r="M11" s="30"/>
       <c r="N11" s="3"/>
       <c r="O11" s="3"/>
       <c r="P11" s="3"/>
@@ -1417,18 +1312,18 @@
       <c r="A12" s="40" t="s">
         <v>22</v>
       </c>
-      <c r="B12" s="33"/>
-      <c r="C12" s="33"/>
-      <c r="D12" s="33"/>
-      <c r="E12" s="33"/>
-      <c r="F12" s="33"/>
-      <c r="G12" s="33"/>
-      <c r="H12" s="33"/>
-      <c r="I12" s="33"/>
-      <c r="J12" s="33"/>
-      <c r="K12" s="33"/>
-      <c r="L12" s="33"/>
-      <c r="M12" s="34"/>
+      <c r="B12" s="30"/>
+      <c r="C12" s="30"/>
+      <c r="D12" s="30"/>
+      <c r="E12" s="30"/>
+      <c r="F12" s="30"/>
+      <c r="G12" s="30"/>
+      <c r="H12" s="30"/>
+      <c r="I12" s="30"/>
+      <c r="J12" s="30"/>
+      <c r="K12" s="30"/>
+      <c r="L12" s="30"/>
+      <c r="M12" s="31"/>
       <c r="N12" s="3"/>
       <c r="O12" s="3"/>
       <c r="P12" s="3"/>
@@ -1454,11 +1349,11 @@
       <c r="C13" s="16" t="s">
         <v>25</v>
       </c>
-      <c r="D13" s="39" t="s">
+      <c r="D13" s="41" t="s">
         <v>26</v>
       </c>
-      <c r="E13" s="33"/>
-      <c r="F13" s="33"/>
+      <c r="E13" s="30"/>
+      <c r="F13" s="30"/>
       <c r="G13" s="17" t="s">
         <v>27</v>
       </c>
@@ -1466,7 +1361,7 @@
         <v>46248</v>
       </c>
       <c r="I13" s="14" t="s">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="J13" s="16" t="s">
         <v>28</v>
@@ -1499,11 +1394,11 @@
       <c r="C14" s="16" t="s">
         <v>31</v>
       </c>
-      <c r="D14" s="39" t="s">
+      <c r="D14" s="41" t="s">
         <v>32</v>
       </c>
-      <c r="E14" s="33"/>
-      <c r="F14" s="33"/>
+      <c r="E14" s="30"/>
+      <c r="F14" s="30"/>
       <c r="G14" s="17" t="s">
         <v>33</v>
       </c>
@@ -1511,7 +1406,7 @@
         <v>46248</v>
       </c>
       <c r="I14" s="14" t="s">
-        <v>7</v>
+        <v>3</v>
       </c>
       <c r="J14" s="16" t="s">
         <v>34</v>
@@ -1520,7 +1415,7 @@
         <v>46248</v>
       </c>
       <c r="L14" s="14" t="s">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="M14" s="17" t="s">
         <v>35</v>
@@ -1544,18 +1439,18 @@
       <c r="A15" s="40" t="s">
         <v>36</v>
       </c>
-      <c r="B15" s="33"/>
-      <c r="C15" s="33"/>
-      <c r="D15" s="33"/>
-      <c r="E15" s="33"/>
-      <c r="F15" s="33"/>
-      <c r="G15" s="33"/>
-      <c r="H15" s="33"/>
-      <c r="I15" s="33"/>
-      <c r="J15" s="33"/>
-      <c r="K15" s="33"/>
-      <c r="L15" s="33"/>
-      <c r="M15" s="34"/>
+      <c r="B15" s="30"/>
+      <c r="C15" s="30"/>
+      <c r="D15" s="30"/>
+      <c r="E15" s="30"/>
+      <c r="F15" s="30"/>
+      <c r="G15" s="30"/>
+      <c r="H15" s="30"/>
+      <c r="I15" s="30"/>
+      <c r="J15" s="30"/>
+      <c r="K15" s="30"/>
+      <c r="L15" s="30"/>
+      <c r="M15" s="31"/>
       <c r="N15" s="3"/>
       <c r="O15" s="3"/>
       <c r="P15" s="3"/>
@@ -1581,11 +1476,11 @@
       <c r="C16" s="16" t="s">
         <v>39</v>
       </c>
-      <c r="D16" s="39" t="s">
+      <c r="D16" s="41" t="s">
         <v>40</v>
       </c>
-      <c r="E16" s="33"/>
-      <c r="F16" s="33"/>
+      <c r="E16" s="30"/>
+      <c r="F16" s="30"/>
       <c r="G16" s="17" t="s">
         <v>41</v>
       </c>
@@ -1593,7 +1488,7 @@
         <v>46248</v>
       </c>
       <c r="I16" s="14" t="s">
-        <v>7</v>
+        <v>3</v>
       </c>
       <c r="J16" s="16" t="s">
         <v>42</v>
@@ -1602,7 +1497,7 @@
         <v>46248</v>
       </c>
       <c r="L16" s="14" t="s">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="M16" s="17" t="s">
         <v>43</v>
@@ -1626,18 +1521,18 @@
       <c r="A17" s="40" t="s">
         <v>44</v>
       </c>
-      <c r="B17" s="33"/>
-      <c r="C17" s="33"/>
-      <c r="D17" s="33"/>
-      <c r="E17" s="33"/>
-      <c r="F17" s="33"/>
-      <c r="G17" s="33"/>
-      <c r="H17" s="33"/>
-      <c r="I17" s="33"/>
-      <c r="J17" s="33"/>
-      <c r="K17" s="33"/>
-      <c r="L17" s="33"/>
-      <c r="M17" s="34"/>
+      <c r="B17" s="30"/>
+      <c r="C17" s="30"/>
+      <c r="D17" s="30"/>
+      <c r="E17" s="30"/>
+      <c r="F17" s="30"/>
+      <c r="G17" s="30"/>
+      <c r="H17" s="30"/>
+      <c r="I17" s="30"/>
+      <c r="J17" s="30"/>
+      <c r="K17" s="30"/>
+      <c r="L17" s="30"/>
+      <c r="M17" s="31"/>
       <c r="N17" s="3"/>
       <c r="O17" s="3"/>
       <c r="P17" s="3"/>
@@ -1653,32 +1548,32 @@
       <c r="Z17" s="3"/>
       <c r="AA17" s="3"/>
     </row>
-    <row r="18" spans="1:27" ht="162" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="18" spans="1:27" ht="141.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A18" s="14" t="s">
         <v>45</v>
       </c>
-      <c r="B18" s="28" t="s">
+      <c r="B18" s="15" t="s">
         <v>46</v>
       </c>
-      <c r="C18" s="27" t="s">
-        <v>96</v>
-      </c>
-      <c r="D18" s="39" t="s">
+      <c r="C18" s="16" t="s">
         <v>47</v>
       </c>
-      <c r="E18" s="33"/>
-      <c r="F18" s="33"/>
+      <c r="D18" s="41" t="s">
+        <v>48</v>
+      </c>
+      <c r="E18" s="30"/>
+      <c r="F18" s="30"/>
       <c r="G18" s="17" t="s">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="H18" s="18">
         <v>46248</v>
       </c>
       <c r="I18" s="14" t="s">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="J18" s="16" t="s">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="K18" s="18"/>
       <c r="L18" s="14"/>
@@ -1700,30 +1595,30 @@
     </row>
     <row r="19" spans="1:27" ht="192.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A19" s="14" t="s">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="B19" s="15" t="s">
-        <v>51</v>
-      </c>
-      <c r="C19" s="27" t="s">
-        <v>97</v>
-      </c>
-      <c r="D19" s="39" t="s">
         <v>52</v>
       </c>
-      <c r="E19" s="33"/>
-      <c r="F19" s="33"/>
+      <c r="C19" s="16" t="s">
+        <v>53</v>
+      </c>
+      <c r="D19" s="41" t="s">
+        <v>54</v>
+      </c>
+      <c r="E19" s="30"/>
+      <c r="F19" s="30"/>
       <c r="G19" s="17" t="s">
-        <v>53</v>
+        <v>55</v>
       </c>
       <c r="H19" s="18">
         <v>46248</v>
       </c>
       <c r="I19" s="14" t="s">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="J19" s="16" t="s">
-        <v>54</v>
+        <v>56</v>
       </c>
       <c r="K19" s="18"/>
       <c r="L19" s="14"/>
@@ -1745,20 +1640,20 @@
     </row>
     <row r="20" spans="1:27" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A20" s="40" t="s">
-        <v>55</v>
+        <v>57</v>
       </c>
-      <c r="B20" s="33"/>
-      <c r="C20" s="33"/>
-      <c r="D20" s="33"/>
-      <c r="E20" s="33"/>
-      <c r="F20" s="33"/>
-      <c r="G20" s="33"/>
-      <c r="H20" s="33"/>
-      <c r="I20" s="33"/>
-      <c r="J20" s="33"/>
-      <c r="K20" s="33"/>
-      <c r="L20" s="33"/>
-      <c r="M20" s="34"/>
+      <c r="B20" s="30"/>
+      <c r="C20" s="30"/>
+      <c r="D20" s="30"/>
+      <c r="E20" s="30"/>
+      <c r="F20" s="30"/>
+      <c r="G20" s="30"/>
+      <c r="H20" s="30"/>
+      <c r="I20" s="30"/>
+      <c r="J20" s="30"/>
+      <c r="K20" s="30"/>
+      <c r="L20" s="30"/>
+      <c r="M20" s="31"/>
       <c r="N20" s="3"/>
       <c r="O20" s="3"/>
       <c r="P20" s="3"/>
@@ -1776,39 +1671,39 @@
     </row>
     <row r="21" spans="1:27" ht="162.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A21" s="14" t="s">
-        <v>56</v>
+        <v>58</v>
       </c>
       <c r="B21" s="15" t="s">
-        <v>57</v>
+        <v>59</v>
       </c>
       <c r="C21" s="16" t="s">
-        <v>58</v>
+        <v>60</v>
       </c>
-      <c r="D21" s="39" t="s">
-        <v>59</v>
+      <c r="D21" s="41" t="s">
+        <v>61</v>
       </c>
-      <c r="E21" s="33"/>
-      <c r="F21" s="33"/>
+      <c r="E21" s="30"/>
+      <c r="F21" s="30"/>
       <c r="G21" s="17" t="s">
-        <v>60</v>
+        <v>62</v>
       </c>
       <c r="H21" s="18">
         <v>46248</v>
       </c>
       <c r="I21" s="14" t="s">
-        <v>7</v>
+        <v>3</v>
       </c>
       <c r="J21" s="16" t="s">
-        <v>61</v>
+        <v>63</v>
       </c>
       <c r="K21" s="18">
         <v>46249</v>
       </c>
       <c r="L21" s="14" t="s">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="M21" s="17" t="s">
-        <v>62</v>
+        <v>64</v>
       </c>
       <c r="N21" s="3"/>
       <c r="O21" s="3"/>
@@ -1827,70 +1722,70 @@
     </row>
     <row r="22" spans="1:27" ht="13.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A22" s="40" t="s">
-        <v>63</v>
+        <v>65</v>
       </c>
-      <c r="B22" s="33"/>
-      <c r="C22" s="33"/>
-      <c r="D22" s="33"/>
-      <c r="E22" s="33"/>
-      <c r="F22" s="33"/>
-      <c r="G22" s="33"/>
-      <c r="H22" s="33"/>
-      <c r="I22" s="33"/>
-      <c r="J22" s="33"/>
-      <c r="K22" s="33"/>
-      <c r="L22" s="33"/>
-      <c r="M22" s="34"/>
+      <c r="B22" s="30"/>
+      <c r="C22" s="30"/>
+      <c r="D22" s="30"/>
+      <c r="E22" s="30"/>
+      <c r="F22" s="30"/>
+      <c r="G22" s="30"/>
+      <c r="H22" s="30"/>
+      <c r="I22" s="30"/>
+      <c r="J22" s="30"/>
+      <c r="K22" s="30"/>
+      <c r="L22" s="30"/>
+      <c r="M22" s="31"/>
       <c r="N22" s="42"/>
-      <c r="O22" s="30"/>
-      <c r="P22" s="30"/>
-      <c r="Q22" s="30"/>
-      <c r="R22" s="30"/>
-      <c r="S22" s="30"/>
-      <c r="T22" s="30"/>
-      <c r="U22" s="30"/>
-      <c r="V22" s="30"/>
-      <c r="W22" s="30"/>
-      <c r="X22" s="30"/>
-      <c r="Y22" s="30"/>
-      <c r="Z22" s="30"/>
+      <c r="O22" s="26"/>
+      <c r="P22" s="26"/>
+      <c r="Q22" s="26"/>
+      <c r="R22" s="26"/>
+      <c r="S22" s="26"/>
+      <c r="T22" s="26"/>
+      <c r="U22" s="26"/>
+      <c r="V22" s="26"/>
+      <c r="W22" s="26"/>
+      <c r="X22" s="26"/>
+      <c r="Y22" s="26"/>
+      <c r="Z22" s="26"/>
       <c r="AA22" s="3"/>
     </row>
     <row r="23" spans="1:27" ht="155.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A23" s="14" t="s">
-        <v>64</v>
+        <v>66</v>
       </c>
       <c r="B23" s="15" t="s">
-        <v>65</v>
+        <v>67</v>
       </c>
       <c r="C23" s="16" t="s">
-        <v>66</v>
+        <v>68</v>
       </c>
-      <c r="D23" s="39" t="s">
-        <v>67</v>
+      <c r="D23" s="41" t="s">
+        <v>69</v>
       </c>
-      <c r="E23" s="33"/>
-      <c r="F23" s="33"/>
+      <c r="E23" s="30"/>
+      <c r="F23" s="30"/>
       <c r="G23" s="23" t="s">
-        <v>68</v>
+        <v>70</v>
       </c>
       <c r="H23" s="18">
         <v>46248</v>
       </c>
       <c r="I23" s="14" t="s">
-        <v>7</v>
+        <v>3</v>
       </c>
       <c r="J23" s="16" t="s">
-        <v>69</v>
+        <v>71</v>
       </c>
       <c r="K23" s="18">
         <v>46249</v>
       </c>
       <c r="L23" s="14" t="s">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="M23" s="17" t="s">
-        <v>70</v>
+        <v>72</v>
       </c>
       <c r="N23" s="3"/>
       <c r="O23" s="3"/>
@@ -1909,61 +1804,61 @@
     </row>
     <row r="24" spans="1:27" ht="13.8" x14ac:dyDescent="0.25">
       <c r="A24" s="40" t="s">
-        <v>71</v>
+        <v>73</v>
       </c>
-      <c r="B24" s="33"/>
-      <c r="C24" s="33"/>
-      <c r="D24" s="33"/>
-      <c r="E24" s="33"/>
-      <c r="F24" s="33"/>
-      <c r="G24" s="33"/>
-      <c r="H24" s="33"/>
-      <c r="I24" s="33"/>
-      <c r="J24" s="33"/>
-      <c r="K24" s="33"/>
-      <c r="L24" s="33"/>
-      <c r="M24" s="34"/>
+      <c r="B24" s="30"/>
+      <c r="C24" s="30"/>
+      <c r="D24" s="30"/>
+      <c r="E24" s="30"/>
+      <c r="F24" s="30"/>
+      <c r="G24" s="30"/>
+      <c r="H24" s="30"/>
+      <c r="I24" s="30"/>
+      <c r="J24" s="30"/>
+      <c r="K24" s="30"/>
+      <c r="L24" s="30"/>
+      <c r="M24" s="31"/>
       <c r="N24" s="43"/>
-      <c r="O24" s="30"/>
-      <c r="P24" s="30"/>
-      <c r="Q24" s="30"/>
-      <c r="R24" s="30"/>
-      <c r="S24" s="30"/>
-      <c r="T24" s="30"/>
-      <c r="U24" s="30"/>
-      <c r="V24" s="30"/>
-      <c r="W24" s="30"/>
-      <c r="X24" s="30"/>
-      <c r="Y24" s="30"/>
-      <c r="Z24" s="30"/>
+      <c r="O24" s="26"/>
+      <c r="P24" s="26"/>
+      <c r="Q24" s="26"/>
+      <c r="R24" s="26"/>
+      <c r="S24" s="26"/>
+      <c r="T24" s="26"/>
+      <c r="U24" s="26"/>
+      <c r="V24" s="26"/>
+      <c r="W24" s="26"/>
+      <c r="X24" s="26"/>
+      <c r="Y24" s="26"/>
+      <c r="Z24" s="26"/>
       <c r="AA24" s="3"/>
     </row>
     <row r="25" spans="1:27" ht="165" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A25" s="14" t="s">
-        <v>72</v>
+        <v>74</v>
       </c>
       <c r="B25" s="15" t="s">
-        <v>98</v>
+        <v>75</v>
       </c>
       <c r="C25" s="16" t="s">
-        <v>99</v>
+        <v>76</v>
       </c>
-      <c r="D25" s="39" t="s">
-        <v>100</v>
+      <c r="D25" s="41" t="s">
+        <v>77</v>
       </c>
-      <c r="E25" s="33"/>
-      <c r="F25" s="33"/>
-      <c r="G25" s="23" t="s">
-        <v>101</v>
+      <c r="E25" s="30"/>
+      <c r="F25" s="30"/>
+      <c r="G25" s="17" t="s">
+        <v>78</v>
       </c>
       <c r="H25" s="18">
         <v>46248</v>
       </c>
-      <c r="I25" s="47" t="s">
-        <v>5</v>
+      <c r="I25" s="14" t="s">
+        <v>2</v>
       </c>
-      <c r="J25" s="27" t="s">
-        <v>102</v>
+      <c r="J25" s="16" t="s">
+        <v>79</v>
       </c>
       <c r="K25" s="18"/>
       <c r="L25" s="14"/>
@@ -1984,31 +1879,31 @@
       <c r="AA25" s="3"/>
     </row>
     <row r="26" spans="1:27" ht="174" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A26" s="47" t="s">
-        <v>73</v>
+      <c r="A26" s="14" t="s">
+        <v>80</v>
       </c>
       <c r="B26" s="15" t="s">
-        <v>74</v>
+        <v>81</v>
       </c>
       <c r="C26" s="16" t="s">
-        <v>75</v>
+        <v>82</v>
       </c>
-      <c r="D26" s="39" t="s">
-        <v>76</v>
+      <c r="D26" s="41" t="s">
+        <v>83</v>
       </c>
-      <c r="E26" s="33"/>
-      <c r="F26" s="33"/>
-      <c r="G26" s="48" t="s">
-        <v>77</v>
+      <c r="E26" s="30"/>
+      <c r="F26" s="30"/>
+      <c r="G26" s="24" t="s">
+        <v>84</v>
       </c>
-      <c r="H26" s="18">
-        <v>46248</v>
+      <c r="H26" s="25" t="s">
+        <v>85</v>
       </c>
       <c r="I26" s="14" t="s">
-        <v>7</v>
+        <v>3</v>
       </c>
       <c r="J26" s="16" t="s">
-        <v>78</v>
+        <v>86</v>
       </c>
       <c r="K26" s="18"/>
       <c r="L26" s="14"/>
@@ -29992,219 +29887,20 @@
     <mergeCell ref="C9:C10"/>
   </mergeCells>
   <hyperlinks>
-    <hyperlink ref="G13" r:id="rId1" xr:uid="{00000000-0004-0000-0B00-000000000000}"/>
-    <hyperlink ref="G14" r:id="rId2" xr:uid="{00000000-0004-0000-0B00-000001000000}"/>
-    <hyperlink ref="M14" r:id="rId3" xr:uid="{00000000-0004-0000-0B00-000002000000}"/>
-    <hyperlink ref="G16" r:id="rId4" xr:uid="{00000000-0004-0000-0B00-000003000000}"/>
-    <hyperlink ref="M16" r:id="rId5" xr:uid="{00000000-0004-0000-0B00-000004000000}"/>
-    <hyperlink ref="G18" r:id="rId6" xr:uid="{00000000-0004-0000-0B00-000005000000}"/>
-    <hyperlink ref="G19" r:id="rId7" xr:uid="{00000000-0004-0000-0B00-000006000000}"/>
-    <hyperlink ref="G21" r:id="rId8" xr:uid="{00000000-0004-0000-0B00-000007000000}"/>
-    <hyperlink ref="M21" r:id="rId9" xr:uid="{00000000-0004-0000-0B00-000008000000}"/>
-    <hyperlink ref="G23" r:id="rId10" xr:uid="{00000000-0004-0000-0B00-000009000000}"/>
-    <hyperlink ref="M23" r:id="rId11" xr:uid="{00000000-0004-0000-0B00-00000A000000}"/>
-    <hyperlink ref="G26" r:id="rId12" xr:uid="{00000000-0004-0000-0B00-00000C000000}"/>
+    <hyperlink ref="G13" r:id="rId1" xr:uid="{00000000-0004-0000-0C00-000000000000}"/>
+    <hyperlink ref="G14" r:id="rId2" xr:uid="{00000000-0004-0000-0C00-000001000000}"/>
+    <hyperlink ref="M14" r:id="rId3" xr:uid="{00000000-0004-0000-0C00-000002000000}"/>
+    <hyperlink ref="G16" r:id="rId4" xr:uid="{00000000-0004-0000-0C00-000003000000}"/>
+    <hyperlink ref="M16" r:id="rId5" xr:uid="{00000000-0004-0000-0C00-000004000000}"/>
+    <hyperlink ref="G18" r:id="rId6" xr:uid="{00000000-0004-0000-0C00-000005000000}"/>
+    <hyperlink ref="G19" r:id="rId7" xr:uid="{00000000-0004-0000-0C00-000006000000}"/>
+    <hyperlink ref="G21" r:id="rId8" xr:uid="{00000000-0004-0000-0C00-000007000000}"/>
+    <hyperlink ref="M21" r:id="rId9" xr:uid="{00000000-0004-0000-0C00-000008000000}"/>
+    <hyperlink ref="G23" r:id="rId10" xr:uid="{00000000-0004-0000-0C00-000009000000}"/>
+    <hyperlink ref="M23" r:id="rId11" xr:uid="{00000000-0004-0000-0C00-00000A000000}"/>
+    <hyperlink ref="G25" r:id="rId12" xr:uid="{00000000-0004-0000-0C00-00000B000000}"/>
+    <hyperlink ref="G26" r:id="rId13" xr:uid="{00000000-0004-0000-0C00-00000C000000}"/>
   </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <pageSetup orientation="portrait" r:id="rId13"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{7FBAECCD-A664-4798-A72B-8871055C7066}">
-  <dimension ref="A1:J10"/>
-  <sheetFormatPr defaultRowHeight="13.8" x14ac:dyDescent="0.25"/>
-  <cols>
-    <col min="1" max="1" width="24.21875" style="25" customWidth="1"/>
-    <col min="2" max="3" width="18.88671875" style="25" customWidth="1"/>
-    <col min="4" max="4" width="24.21875" style="25" customWidth="1"/>
-    <col min="5" max="5" width="19.33203125" style="25" customWidth="1"/>
-    <col min="6" max="6" width="17" style="25" customWidth="1"/>
-    <col min="7" max="7" width="17.21875" style="25" customWidth="1"/>
-    <col min="8" max="8" width="17.109375" style="25" customWidth="1"/>
-    <col min="9" max="9" width="26.6640625" style="25" customWidth="1"/>
-    <col min="10" max="10" width="33.77734375" style="25" customWidth="1"/>
-    <col min="11" max="16384" width="8.88671875" style="25"/>
-  </cols>
-  <sheetData>
-    <row r="1" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A1" s="24" t="s">
-        <v>79</v>
-      </c>
-      <c r="B1" s="24" t="s">
-        <v>83</v>
-      </c>
-      <c r="C1" s="24" t="s">
-        <v>80</v>
-      </c>
-      <c r="D1" s="24" t="s">
-        <v>81</v>
-      </c>
-      <c r="E1" s="24" t="s">
-        <v>82</v>
-      </c>
-      <c r="F1" s="24" t="s">
-        <v>88</v>
-      </c>
-      <c r="G1" s="24" t="s">
-        <v>89</v>
-      </c>
-      <c r="H1" s="24" t="s">
-        <v>90</v>
-      </c>
-      <c r="I1" s="24" t="s">
-        <v>91</v>
-      </c>
-      <c r="J1" s="24" t="s">
-        <v>92</v>
-      </c>
-    </row>
-    <row r="2" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A2" s="26" t="s">
-        <v>23</v>
-      </c>
-      <c r="B2" s="26" t="s">
-        <v>84</v>
-      </c>
-      <c r="C2" s="26" t="s">
-        <v>85</v>
-      </c>
-      <c r="D2" s="26" t="s">
-        <v>86</v>
-      </c>
-      <c r="E2" s="26" t="s">
-        <v>87</v>
-      </c>
-      <c r="F2" s="26" t="s">
-        <v>95</v>
-      </c>
-      <c r="G2" s="26" t="s">
-        <v>85</v>
-      </c>
-      <c r="H2" s="26">
-        <v>1</v>
-      </c>
-      <c r="I2" s="26" t="s">
-        <v>94</v>
-      </c>
-      <c r="J2" s="26" t="s">
-        <v>93</v>
-      </c>
-    </row>
-    <row r="3" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A3" s="26" t="s">
-        <v>29</v>
-      </c>
-      <c r="B3" s="26"/>
-      <c r="C3" s="26"/>
-      <c r="D3" s="26"/>
-      <c r="E3" s="26"/>
-      <c r="F3" s="26"/>
-      <c r="G3" s="26"/>
-      <c r="H3" s="26"/>
-      <c r="I3" s="26"/>
-      <c r="J3" s="26"/>
-    </row>
-    <row r="4" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A4" s="26" t="s">
-        <v>37</v>
-      </c>
-      <c r="B4" s="26"/>
-      <c r="C4" s="26"/>
-      <c r="D4" s="26"/>
-      <c r="E4" s="26"/>
-      <c r="F4" s="26"/>
-      <c r="G4" s="26"/>
-      <c r="H4" s="26"/>
-      <c r="I4" s="26"/>
-      <c r="J4" s="26"/>
-    </row>
-    <row r="5" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A5" s="26" t="s">
-        <v>45</v>
-      </c>
-      <c r="B5" s="26"/>
-      <c r="C5" s="26"/>
-      <c r="D5" s="26"/>
-      <c r="E5" s="26"/>
-      <c r="F5" s="26"/>
-      <c r="G5" s="26"/>
-      <c r="H5" s="26"/>
-      <c r="I5" s="26"/>
-      <c r="J5" s="26"/>
-    </row>
-    <row r="6" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A6" s="26" t="s">
-        <v>50</v>
-      </c>
-      <c r="B6" s="26"/>
-      <c r="C6" s="26"/>
-      <c r="D6" s="26"/>
-      <c r="E6" s="26"/>
-      <c r="F6" s="26"/>
-      <c r="G6" s="26"/>
-      <c r="H6" s="26"/>
-      <c r="I6" s="26"/>
-      <c r="J6" s="26"/>
-    </row>
-    <row r="7" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A7" s="26" t="s">
-        <v>56</v>
-      </c>
-      <c r="B7" s="26"/>
-      <c r="C7" s="26"/>
-      <c r="D7" s="26"/>
-      <c r="E7" s="26"/>
-      <c r="F7" s="26"/>
-      <c r="G7" s="26"/>
-      <c r="H7" s="26"/>
-      <c r="I7" s="26"/>
-      <c r="J7" s="26"/>
-    </row>
-    <row r="8" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A8" s="26" t="s">
-        <v>64</v>
-      </c>
-      <c r="B8" s="26"/>
-      <c r="C8" s="26"/>
-      <c r="D8" s="26"/>
-      <c r="E8" s="26"/>
-      <c r="F8" s="26"/>
-      <c r="G8" s="26"/>
-      <c r="H8" s="26"/>
-      <c r="I8" s="26"/>
-      <c r="J8" s="26"/>
-    </row>
-    <row r="9" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A9" s="26" t="s">
-        <v>72</v>
-      </c>
-      <c r="B9" s="26"/>
-      <c r="C9" s="26"/>
-      <c r="D9" s="26"/>
-      <c r="E9" s="26"/>
-      <c r="F9" s="26"/>
-      <c r="G9" s="26"/>
-      <c r="H9" s="26"/>
-      <c r="I9" s="26"/>
-      <c r="J9" s="26"/>
-    </row>
-    <row r="10" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A10" s="26" t="s">
-        <v>73</v>
-      </c>
-      <c r="B10" s="26"/>
-      <c r="C10" s="26"/>
-      <c r="D10" s="26"/>
-      <c r="E10" s="26"/>
-      <c r="F10" s="26"/>
-      <c r="G10" s="26"/>
-      <c r="H10" s="26"/>
-      <c r="I10" s="26"/>
-      <c r="J10" s="26"/>
-    </row>
-  </sheetData>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <pageSetup orientation="portrait" r:id="rId1"/>
 </worksheet>
 </file>